--- a/automation/reports/Excel/Automation_Test_Report.xlsx
+++ b/automation/reports/Excel/Automation_Test_Report.xlsx
@@ -2959,7 +2959,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>16.16 seconds</t>
+    <t>16.75 seconds</t>
   </si>
   <si>
     <t>Environment Details</t>
@@ -2992,7 +2992,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>23/6/2026, 3:34:25 pm</t>
+    <t>23/7/2026, 2:54:00 pm</t>
   </si>
   <si>
     <t>Defect ID</t>
@@ -3567,7 +3567,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>10</v>
@@ -3587,7 +3587,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -3607,7 +3607,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>15</v>
@@ -3627,7 +3627,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>18</v>
@@ -3647,7 +3647,7 @@
         <v>9</v>
       </c>
       <c r="E6" s="2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>21</v>
@@ -3667,7 +3667,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="2">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
@@ -3687,7 +3687,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="2">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
@@ -3707,7 +3707,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -3727,7 +3727,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
@@ -3747,7 +3747,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>21</v>
@@ -3767,7 +3767,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>10</v>
@@ -3787,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="2">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>15</v>
@@ -3807,7 +3807,7 @@
         <v>9</v>
       </c>
       <c r="E14" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>15</v>
@@ -3827,7 +3827,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="2">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
@@ -3847,7 +3847,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>21</v>
@@ -3867,7 +3867,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
@@ -3887,7 +3887,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>15</v>
@@ -3907,7 +3907,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>15</v>
@@ -3927,7 +3927,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
@@ -3947,7 +3947,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="2">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>21</v>
@@ -3967,7 +3967,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="2">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -3987,7 +3987,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>15</v>
@@ -4007,7 +4007,7 @@
         <v>9</v>
       </c>
       <c r="E24" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>15</v>
@@ -4027,7 +4027,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>18</v>
@@ -4047,7 +4047,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>21</v>
@@ -4067,7 +4067,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -4087,7 +4087,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>15</v>
@@ -4107,7 +4107,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>15</v>
@@ -4127,7 +4127,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
@@ -4147,7 +4147,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="2">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>21</v>
@@ -4167,7 +4167,7 @@
         <v>9</v>
       </c>
       <c r="E32" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -4187,7 +4187,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>15</v>
@@ -4207,7 +4207,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="2">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>15</v>
@@ -4227,7 +4227,7 @@
         <v>9</v>
       </c>
       <c r="E35" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>18</v>
@@ -4247,7 +4247,7 @@
         <v>9</v>
       </c>
       <c r="E36" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>21</v>
@@ -4267,7 +4267,7 @@
         <v>9</v>
       </c>
       <c r="E37" s="2">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>10</v>
@@ -4287,7 +4287,7 @@
         <v>9</v>
       </c>
       <c r="E38" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>15</v>
@@ -4307,7 +4307,7 @@
         <v>9</v>
       </c>
       <c r="E39" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>15</v>
@@ -4327,7 +4327,7 @@
         <v>9</v>
       </c>
       <c r="E40" s="2">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>18</v>
@@ -4347,7 +4347,7 @@
         <v>9</v>
       </c>
       <c r="E41" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>21</v>
@@ -4367,7 +4367,7 @@
         <v>9</v>
       </c>
       <c r="E42" s="2">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -4387,7 +4387,7 @@
         <v>9</v>
       </c>
       <c r="E43" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>15</v>
@@ -4407,7 +4407,7 @@
         <v>9</v>
       </c>
       <c r="E44" s="2">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>15</v>
@@ -4427,7 +4427,7 @@
         <v>9</v>
       </c>
       <c r="E45" s="2">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>18</v>
@@ -4447,7 +4447,7 @@
         <v>9</v>
       </c>
       <c r="E46" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>21</v>
@@ -4467,7 +4467,7 @@
         <v>9</v>
       </c>
       <c r="E47" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -4487,7 +4487,7 @@
         <v>9</v>
       </c>
       <c r="E48" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>15</v>
@@ -4507,7 +4507,7 @@
         <v>9</v>
       </c>
       <c r="E49" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>15</v>
@@ -4527,7 +4527,7 @@
         <v>9</v>
       </c>
       <c r="E50" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>18</v>
@@ -4547,7 +4547,7 @@
         <v>9</v>
       </c>
       <c r="E51" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>21</v>
@@ -4567,7 +4567,7 @@
         <v>9</v>
       </c>
       <c r="E52" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -4587,7 +4587,7 @@
         <v>9</v>
       </c>
       <c r="E53" s="2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>15</v>
@@ -4607,7 +4607,7 @@
         <v>9</v>
       </c>
       <c r="E54" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>15</v>
@@ -4627,7 +4627,7 @@
         <v>9</v>
       </c>
       <c r="E55" s="2">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>18</v>
@@ -4647,7 +4647,7 @@
         <v>9</v>
       </c>
       <c r="E56" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>21</v>
@@ -4667,7 +4667,7 @@
         <v>9</v>
       </c>
       <c r="E57" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -4687,7 +4687,7 @@
         <v>9</v>
       </c>
       <c r="E58" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>15</v>
@@ -4707,7 +4707,7 @@
         <v>9</v>
       </c>
       <c r="E59" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>9</v>
       </c>
       <c r="E60" s="2">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>18</v>
@@ -4747,7 +4747,7 @@
         <v>9</v>
       </c>
       <c r="E61" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>21</v>
@@ -4767,7 +4767,7 @@
         <v>9</v>
       </c>
       <c r="E62" s="2">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -4787,7 +4787,7 @@
         <v>9</v>
       </c>
       <c r="E63" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>15</v>
@@ -4807,7 +4807,7 @@
         <v>9</v>
       </c>
       <c r="E64" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>15</v>
@@ -4827,7 +4827,7 @@
         <v>9</v>
       </c>
       <c r="E65" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>18</v>
@@ -4867,7 +4867,7 @@
         <v>9</v>
       </c>
       <c r="E67" s="2">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -4887,7 +4887,7 @@
         <v>9</v>
       </c>
       <c r="E68" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>15</v>
@@ -4907,7 +4907,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>15</v>
@@ -4927,7 +4927,7 @@
         <v>9</v>
       </c>
       <c r="E70" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>18</v>
@@ -4947,7 +4947,7 @@
         <v>9</v>
       </c>
       <c r="E71" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>21</v>
@@ -4967,7 +4967,7 @@
         <v>9</v>
       </c>
       <c r="E72" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -4987,7 +4987,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="2">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>15</v>
@@ -5007,7 +5007,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>15</v>
@@ -5027,7 +5027,7 @@
         <v>9</v>
       </c>
       <c r="E75" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>18</v>
@@ -5047,7 +5047,7 @@
         <v>9</v>
       </c>
       <c r="E76" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>21</v>
@@ -5067,7 +5067,7 @@
         <v>9</v>
       </c>
       <c r="E77" s="2">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -5087,7 +5087,7 @@
         <v>9</v>
       </c>
       <c r="E78" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>15</v>
@@ -5107,7 +5107,7 @@
         <v>9</v>
       </c>
       <c r="E79" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>15</v>
@@ -5127,7 +5127,7 @@
         <v>9</v>
       </c>
       <c r="E80" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>18</v>
@@ -5147,7 +5147,7 @@
         <v>9</v>
       </c>
       <c r="E81" s="2">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>21</v>
@@ -5167,7 +5167,7 @@
         <v>9</v>
       </c>
       <c r="E82" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -5187,7 +5187,7 @@
         <v>9</v>
       </c>
       <c r="E83" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>15</v>
@@ -5207,7 +5207,7 @@
         <v>9</v>
       </c>
       <c r="E84" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>15</v>
@@ -5227,7 +5227,7 @@
         <v>9</v>
       </c>
       <c r="E85" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>18</v>
@@ -5247,7 +5247,7 @@
         <v>9</v>
       </c>
       <c r="E86" s="2">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>21</v>
@@ -5267,7 +5267,7 @@
         <v>9</v>
       </c>
       <c r="E87" s="2">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -5287,7 +5287,7 @@
         <v>9</v>
       </c>
       <c r="E88" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>15</v>
@@ -5307,7 +5307,7 @@
         <v>9</v>
       </c>
       <c r="E89" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>15</v>
@@ -5327,7 +5327,7 @@
         <v>9</v>
       </c>
       <c r="E90" s="2">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>18</v>
@@ -5347,7 +5347,7 @@
         <v>9</v>
       </c>
       <c r="E91" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>21</v>
@@ -5367,7 +5367,7 @@
         <v>9</v>
       </c>
       <c r="E92" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -5387,7 +5387,7 @@
         <v>9</v>
       </c>
       <c r="E93" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>15</v>
@@ -5407,7 +5407,7 @@
         <v>9</v>
       </c>
       <c r="E94" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>15</v>
@@ -5427,7 +5427,7 @@
         <v>9</v>
       </c>
       <c r="E95" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>18</v>
@@ -5447,7 +5447,7 @@
         <v>9</v>
       </c>
       <c r="E96" s="2">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>21</v>
@@ -5467,7 +5467,7 @@
         <v>9</v>
       </c>
       <c r="E97" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -5507,7 +5507,7 @@
         <v>9</v>
       </c>
       <c r="E99" s="2">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>15</v>
@@ -5527,7 +5527,7 @@
         <v>9</v>
       </c>
       <c r="E100" s="2">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>18</v>
@@ -5547,7 +5547,7 @@
         <v>9</v>
       </c>
       <c r="E101" s="2">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>21</v>
@@ -5567,7 +5567,7 @@
         <v>9</v>
       </c>
       <c r="E102" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -5587,7 +5587,7 @@
         <v>9</v>
       </c>
       <c r="E103" s="2">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>15</v>
@@ -5607,7 +5607,7 @@
         <v>9</v>
       </c>
       <c r="E104" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>15</v>
@@ -5627,7 +5627,7 @@
         <v>9</v>
       </c>
       <c r="E105" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>18</v>
@@ -5647,7 +5647,7 @@
         <v>9</v>
       </c>
       <c r="E106" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>21</v>
@@ -5667,7 +5667,7 @@
         <v>9</v>
       </c>
       <c r="E107" s="2">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -5687,7 +5687,7 @@
         <v>9</v>
       </c>
       <c r="E108" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>15</v>
@@ -5707,7 +5707,7 @@
         <v>9</v>
       </c>
       <c r="E109" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>15</v>
@@ -5727,7 +5727,7 @@
         <v>9</v>
       </c>
       <c r="E110" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>18</v>
@@ -5747,7 +5747,7 @@
         <v>9</v>
       </c>
       <c r="E111" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>21</v>
@@ -5767,7 +5767,7 @@
         <v>9</v>
       </c>
       <c r="E112" s="2">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -5787,7 +5787,7 @@
         <v>9</v>
       </c>
       <c r="E113" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>15</v>
@@ -5807,7 +5807,7 @@
         <v>9</v>
       </c>
       <c r="E114" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>15</v>
@@ -5827,7 +5827,7 @@
         <v>9</v>
       </c>
       <c r="E115" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>18</v>
@@ -5847,7 +5847,7 @@
         <v>9</v>
       </c>
       <c r="E116" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>21</v>
@@ -5867,7 +5867,7 @@
         <v>9</v>
       </c>
       <c r="E117" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -5887,7 +5887,7 @@
         <v>9</v>
       </c>
       <c r="E118" s="2">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>15</v>
@@ -5907,7 +5907,7 @@
         <v>9</v>
       </c>
       <c r="E119" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>15</v>
@@ -5927,7 +5927,7 @@
         <v>9</v>
       </c>
       <c r="E120" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>18</v>
@@ -5947,7 +5947,7 @@
         <v>9</v>
       </c>
       <c r="E121" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>21</v>
@@ -5967,7 +5967,7 @@
         <v>9</v>
       </c>
       <c r="E122" s="2">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -5987,7 +5987,7 @@
         <v>9</v>
       </c>
       <c r="E123" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>15</v>
@@ -6007,7 +6007,7 @@
         <v>9</v>
       </c>
       <c r="E124" s="2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>15</v>
@@ -6027,7 +6027,7 @@
         <v>9</v>
       </c>
       <c r="E125" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>18</v>
@@ -6047,7 +6047,7 @@
         <v>9</v>
       </c>
       <c r="E126" s="2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>21</v>
@@ -6067,7 +6067,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -6087,7 +6087,7 @@
         <v>9</v>
       </c>
       <c r="E128" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>15</v>
@@ -6107,7 +6107,7 @@
         <v>9</v>
       </c>
       <c r="E129" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>15</v>
@@ -6127,7 +6127,7 @@
         <v>9</v>
       </c>
       <c r="E130" s="2">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>18</v>
@@ -6147,7 +6147,7 @@
         <v>9</v>
       </c>
       <c r="E131" s="2">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>21</v>
@@ -6187,7 +6187,7 @@
         <v>9</v>
       </c>
       <c r="E133" s="2">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>15</v>
@@ -6207,7 +6207,7 @@
         <v>9</v>
       </c>
       <c r="E134" s="2">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>15</v>
@@ -6227,7 +6227,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="2">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>18</v>
@@ -6247,7 +6247,7 @@
         <v>9</v>
       </c>
       <c r="E136" s="2">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>21</v>
@@ -6267,7 +6267,7 @@
         <v>9</v>
       </c>
       <c r="E137" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
@@ -6287,7 +6287,7 @@
         <v>9</v>
       </c>
       <c r="E138" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>15</v>
@@ -6307,7 +6307,7 @@
         <v>9</v>
       </c>
       <c r="E139" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>15</v>
@@ -6327,7 +6327,7 @@
         <v>9</v>
       </c>
       <c r="E140" s="2">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>18</v>
@@ -6347,7 +6347,7 @@
         <v>9</v>
       </c>
       <c r="E141" s="2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>21</v>
@@ -6367,7 +6367,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -6387,7 +6387,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>15</v>
@@ -6407,7 +6407,7 @@
         <v>9</v>
       </c>
       <c r="E144" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>15</v>
@@ -6427,7 +6427,7 @@
         <v>9</v>
       </c>
       <c r="E145" s="2">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>18</v>
@@ -6447,7 +6447,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>21</v>
@@ -6467,7 +6467,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
@@ -6487,7 +6487,7 @@
         <v>9</v>
       </c>
       <c r="E148" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>15</v>
@@ -6507,7 +6507,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>15</v>
@@ -6527,7 +6527,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="2">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>18</v>
@@ -6547,7 +6547,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="2">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>21</v>
@@ -6567,7 +6567,7 @@
         <v>9</v>
       </c>
       <c r="E152" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
@@ -6587,7 +6587,7 @@
         <v>9</v>
       </c>
       <c r="E153" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>15</v>
@@ -6607,7 +6607,7 @@
         <v>9</v>
       </c>
       <c r="E154" s="2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>15</v>
@@ -6627,7 +6627,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>18</v>
@@ -6647,7 +6647,7 @@
         <v>9</v>
       </c>
       <c r="E156" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>21</v>
@@ -6667,7 +6667,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>10</v>
@@ -6687,7 +6687,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>15</v>
@@ -6707,7 +6707,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>15</v>
@@ -6727,7 +6727,7 @@
         <v>9</v>
       </c>
       <c r="E160" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>18</v>
@@ -6747,7 +6747,7 @@
         <v>9</v>
       </c>
       <c r="E161" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>21</v>
@@ -6767,7 +6767,7 @@
         <v>9</v>
       </c>
       <c r="E162" s="2">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>9</v>
       </c>
       <c r="E163" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>15</v>
@@ -6807,7 +6807,7 @@
         <v>9</v>
       </c>
       <c r="E164" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>15</v>
@@ -6827,7 +6827,7 @@
         <v>9</v>
       </c>
       <c r="E165" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>18</v>
@@ -6847,7 +6847,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>21</v>
@@ -6867,7 +6867,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>10</v>
@@ -6887,7 +6887,7 @@
         <v>9</v>
       </c>
       <c r="E168" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>15</v>
@@ -6907,7 +6907,7 @@
         <v>9</v>
       </c>
       <c r="E169" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>15</v>
@@ -6927,7 +6927,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="2">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>18</v>
@@ -6947,7 +6947,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="2">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>21</v>
@@ -6967,7 +6967,7 @@
         <v>9</v>
       </c>
       <c r="E172" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
@@ -6987,7 +6987,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>15</v>
@@ -7007,7 +7007,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>15</v>
@@ -7027,7 +7027,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>18</v>
@@ -7047,7 +7047,7 @@
         <v>9</v>
       </c>
       <c r="E176" s="2">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>21</v>
@@ -7067,7 +7067,7 @@
         <v>9</v>
       </c>
       <c r="E177" s="2">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>10</v>
@@ -7087,7 +7087,7 @@
         <v>9</v>
       </c>
       <c r="E178" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>15</v>
@@ -7107,7 +7107,7 @@
         <v>9</v>
       </c>
       <c r="E179" s="2">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>15</v>
@@ -7127,7 +7127,7 @@
         <v>9</v>
       </c>
       <c r="E180" s="2">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>18</v>
@@ -7147,7 +7147,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>21</v>
@@ -7167,7 +7167,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>10</v>
@@ -7187,7 +7187,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>15</v>
@@ -7207,7 +7207,7 @@
         <v>9</v>
       </c>
       <c r="E184" s="2">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>15</v>
@@ -7227,7 +7227,7 @@
         <v>9</v>
       </c>
       <c r="E185" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>18</v>
@@ -7247,7 +7247,7 @@
         <v>9</v>
       </c>
       <c r="E186" s="2">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>21</v>
@@ -7267,7 +7267,7 @@
         <v>9</v>
       </c>
       <c r="E187" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>10</v>
@@ -7287,7 +7287,7 @@
         <v>9</v>
       </c>
       <c r="E188" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>15</v>
@@ -7307,7 +7307,7 @@
         <v>9</v>
       </c>
       <c r="E189" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>15</v>
@@ -7327,7 +7327,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="2">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>18</v>
@@ -7347,7 +7347,7 @@
         <v>9</v>
       </c>
       <c r="E191" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>21</v>
@@ -7367,7 +7367,7 @@
         <v>9</v>
       </c>
       <c r="E192" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>10</v>
@@ -7387,7 +7387,7 @@
         <v>9</v>
       </c>
       <c r="E193" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>15</v>
@@ -7407,7 +7407,7 @@
         <v>9</v>
       </c>
       <c r="E194" s="2">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>15</v>
@@ -7427,7 +7427,7 @@
         <v>9</v>
       </c>
       <c r="E195" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>18</v>
@@ -7447,7 +7447,7 @@
         <v>9</v>
       </c>
       <c r="E196" s="2">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>21</v>
@@ -7467,7 +7467,7 @@
         <v>9</v>
       </c>
       <c r="E197" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>10</v>
@@ -7487,7 +7487,7 @@
         <v>9</v>
       </c>
       <c r="E198" s="2">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>15</v>
@@ -7507,7 +7507,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>15</v>
@@ -7527,7 +7527,7 @@
         <v>9</v>
       </c>
       <c r="E200" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>18</v>
@@ -7547,7 +7547,7 @@
         <v>9</v>
       </c>
       <c r="E201" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>21</v>
@@ -7567,7 +7567,7 @@
         <v>9</v>
       </c>
       <c r="E202" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>10</v>
@@ -7587,7 +7587,7 @@
         <v>9</v>
       </c>
       <c r="E203" s="2">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>15</v>
@@ -7607,7 +7607,7 @@
         <v>9</v>
       </c>
       <c r="E204" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>15</v>
@@ -7627,7 +7627,7 @@
         <v>9</v>
       </c>
       <c r="E205" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>18</v>
@@ -7647,7 +7647,7 @@
         <v>9</v>
       </c>
       <c r="E206" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>21</v>
@@ -7667,7 +7667,7 @@
         <v>9</v>
       </c>
       <c r="E207" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>10</v>
@@ -7687,7 +7687,7 @@
         <v>9</v>
       </c>
       <c r="E208" s="2">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>15</v>
@@ -7707,7 +7707,7 @@
         <v>9</v>
       </c>
       <c r="E209" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>15</v>
@@ -7727,7 +7727,7 @@
         <v>9</v>
       </c>
       <c r="E210" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>18</v>
@@ -7767,7 +7767,7 @@
         <v>9</v>
       </c>
       <c r="E212" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>10</v>
@@ -7787,7 +7787,7 @@
         <v>9</v>
       </c>
       <c r="E213" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>15</v>
@@ -7807,7 +7807,7 @@
         <v>9</v>
       </c>
       <c r="E214" s="2">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>15</v>
@@ -7827,7 +7827,7 @@
         <v>9</v>
       </c>
       <c r="E215" s="2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>18</v>
@@ -7847,7 +7847,7 @@
         <v>9</v>
       </c>
       <c r="E216" s="2">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>21</v>
@@ -7867,7 +7867,7 @@
         <v>9</v>
       </c>
       <c r="E217" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>10</v>
@@ -7887,7 +7887,7 @@
         <v>9</v>
       </c>
       <c r="E218" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>15</v>
@@ -7907,7 +7907,7 @@
         <v>9</v>
       </c>
       <c r="E219" s="2">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>9</v>
       </c>
       <c r="E220" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>18</v>
@@ -7947,7 +7947,7 @@
         <v>9</v>
       </c>
       <c r="E221" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>21</v>
@@ -7967,7 +7967,7 @@
         <v>9</v>
       </c>
       <c r="E222" s="2">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>10</v>
@@ -7987,7 +7987,7 @@
         <v>9</v>
       </c>
       <c r="E223" s="2">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>15</v>
@@ -8007,7 +8007,7 @@
         <v>9</v>
       </c>
       <c r="E224" s="2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>15</v>
@@ -8027,7 +8027,7 @@
         <v>9</v>
       </c>
       <c r="E225" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>18</v>
@@ -8047,7 +8047,7 @@
         <v>9</v>
       </c>
       <c r="E226" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>21</v>
@@ -8067,7 +8067,7 @@
         <v>9</v>
       </c>
       <c r="E227" s="2">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>10</v>
@@ -8087,7 +8087,7 @@
         <v>9</v>
       </c>
       <c r="E228" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>15</v>
@@ -8107,7 +8107,7 @@
         <v>9</v>
       </c>
       <c r="E229" s="2">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>15</v>
@@ -8127,7 +8127,7 @@
         <v>9</v>
       </c>
       <c r="E230" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>18</v>
@@ -8147,7 +8147,7 @@
         <v>9</v>
       </c>
       <c r="E231" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>21</v>
@@ -8167,7 +8167,7 @@
         <v>9</v>
       </c>
       <c r="E232" s="2">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>10</v>
@@ -8187,7 +8187,7 @@
         <v>9</v>
       </c>
       <c r="E233" s="2">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>15</v>
@@ -8207,7 +8207,7 @@
         <v>9</v>
       </c>
       <c r="E234" s="2">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>15</v>
@@ -8227,7 +8227,7 @@
         <v>9</v>
       </c>
       <c r="E235" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>18</v>
@@ -8247,7 +8247,7 @@
         <v>9</v>
       </c>
       <c r="E236" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>21</v>
@@ -8267,7 +8267,7 @@
         <v>9</v>
       </c>
       <c r="E237" s="2">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>10</v>
@@ -8287,7 +8287,7 @@
         <v>9</v>
       </c>
       <c r="E238" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>15</v>
@@ -8307,7 +8307,7 @@
         <v>9</v>
       </c>
       <c r="E239" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>15</v>
@@ -8327,7 +8327,7 @@
         <v>9</v>
       </c>
       <c r="E240" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>18</v>
@@ -8347,7 +8347,7 @@
         <v>9</v>
       </c>
       <c r="E241" s="2">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>21</v>
@@ -8367,7 +8367,7 @@
         <v>9</v>
       </c>
       <c r="E242" s="2">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>10</v>
@@ -8387,7 +8387,7 @@
         <v>9</v>
       </c>
       <c r="E243" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>15</v>
@@ -8407,7 +8407,7 @@
         <v>9</v>
       </c>
       <c r="E244" s="2">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>15</v>
@@ -8427,7 +8427,7 @@
         <v>9</v>
       </c>
       <c r="E245" s="2">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>18</v>
@@ -8447,7 +8447,7 @@
         <v>9</v>
       </c>
       <c r="E246" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>21</v>
@@ -8467,7 +8467,7 @@
         <v>9</v>
       </c>
       <c r="E247" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>10</v>
@@ -8487,7 +8487,7 @@
         <v>9</v>
       </c>
       <c r="E248" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>15</v>
@@ -8507,7 +8507,7 @@
         <v>9</v>
       </c>
       <c r="E249" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>15</v>
@@ -8527,7 +8527,7 @@
         <v>9</v>
       </c>
       <c r="E250" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>18</v>
@@ -8547,7 +8547,7 @@
         <v>9</v>
       </c>
       <c r="E251" s="2">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>21</v>
@@ -8567,7 +8567,7 @@
         <v>9</v>
       </c>
       <c r="E252" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>10</v>
@@ -8587,7 +8587,7 @@
         <v>9</v>
       </c>
       <c r="E253" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>15</v>
@@ -8607,7 +8607,7 @@
         <v>9</v>
       </c>
       <c r="E254" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>15</v>
@@ -8627,7 +8627,7 @@
         <v>9</v>
       </c>
       <c r="E255" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>18</v>
@@ -8647,7 +8647,7 @@
         <v>9</v>
       </c>
       <c r="E256" s="2">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>21</v>
@@ -8667,7 +8667,7 @@
         <v>9</v>
       </c>
       <c r="E257" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>10</v>
@@ -8687,7 +8687,7 @@
         <v>9</v>
       </c>
       <c r="E258" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>15</v>
@@ -8707,7 +8707,7 @@
         <v>9</v>
       </c>
       <c r="E259" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>15</v>
@@ -8727,7 +8727,7 @@
         <v>9</v>
       </c>
       <c r="E260" s="2">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>18</v>
@@ -8747,7 +8747,7 @@
         <v>9</v>
       </c>
       <c r="E261" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>21</v>
@@ -8767,7 +8767,7 @@
         <v>9</v>
       </c>
       <c r="E262" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>10</v>
@@ -8787,7 +8787,7 @@
         <v>9</v>
       </c>
       <c r="E263" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>15</v>
@@ -8807,7 +8807,7 @@
         <v>9</v>
       </c>
       <c r="E264" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>15</v>
@@ -8827,7 +8827,7 @@
         <v>9</v>
       </c>
       <c r="E265" s="2">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>18</v>
@@ -8847,7 +8847,7 @@
         <v>9</v>
       </c>
       <c r="E266" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>21</v>
@@ -8867,7 +8867,7 @@
         <v>9</v>
       </c>
       <c r="E267" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>10</v>
@@ -8887,7 +8887,7 @@
         <v>9</v>
       </c>
       <c r="E268" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>15</v>
@@ -8907,7 +8907,7 @@
         <v>9</v>
       </c>
       <c r="E269" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>15</v>
@@ -8927,7 +8927,7 @@
         <v>9</v>
       </c>
       <c r="E270" s="2">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>18</v>
@@ -8947,7 +8947,7 @@
         <v>9</v>
       </c>
       <c r="E271" s="2">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>21</v>
@@ -8967,7 +8967,7 @@
         <v>9</v>
       </c>
       <c r="E272" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>10</v>
@@ -8987,7 +8987,7 @@
         <v>9</v>
       </c>
       <c r="E273" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>15</v>
@@ -9007,7 +9007,7 @@
         <v>9</v>
       </c>
       <c r="E274" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>15</v>
@@ -9027,7 +9027,7 @@
         <v>9</v>
       </c>
       <c r="E275" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>18</v>
@@ -9047,7 +9047,7 @@
         <v>9</v>
       </c>
       <c r="E276" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>21</v>
@@ -9067,7 +9067,7 @@
         <v>9</v>
       </c>
       <c r="E277" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>10</v>
@@ -9087,7 +9087,7 @@
         <v>9</v>
       </c>
       <c r="E278" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>15</v>
@@ -9107,7 +9107,7 @@
         <v>9</v>
       </c>
       <c r="E279" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>15</v>
@@ -9127,7 +9127,7 @@
         <v>9</v>
       </c>
       <c r="E280" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>18</v>
@@ -9147,7 +9147,7 @@
         <v>9</v>
       </c>
       <c r="E281" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>21</v>
@@ -9187,7 +9187,7 @@
         <v>9</v>
       </c>
       <c r="E283" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>15</v>
@@ -9207,7 +9207,7 @@
         <v>9</v>
       </c>
       <c r="E284" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>15</v>
@@ -9227,7 +9227,7 @@
         <v>9</v>
       </c>
       <c r="E285" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>18</v>
@@ -9247,7 +9247,7 @@
         <v>9</v>
       </c>
       <c r="E286" s="2">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>21</v>
@@ -9267,7 +9267,7 @@
         <v>9</v>
       </c>
       <c r="E287" s="2">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>10</v>
@@ -9287,7 +9287,7 @@
         <v>9</v>
       </c>
       <c r="E288" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>15</v>
@@ -9307,7 +9307,7 @@
         <v>9</v>
       </c>
       <c r="E289" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>15</v>
@@ -9327,7 +9327,7 @@
         <v>9</v>
       </c>
       <c r="E290" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>18</v>
@@ -9347,7 +9347,7 @@
         <v>9</v>
       </c>
       <c r="E291" s="2">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>21</v>
@@ -9367,7 +9367,7 @@
         <v>9</v>
       </c>
       <c r="E292" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>10</v>
@@ -9387,7 +9387,7 @@
         <v>9</v>
       </c>
       <c r="E293" s="2">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>15</v>
@@ -9407,7 +9407,7 @@
         <v>9</v>
       </c>
       <c r="E294" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>15</v>
@@ -9427,7 +9427,7 @@
         <v>9</v>
       </c>
       <c r="E295" s="2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>18</v>
@@ -9447,7 +9447,7 @@
         <v>9</v>
       </c>
       <c r="E296" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>21</v>
@@ -9467,7 +9467,7 @@
         <v>9</v>
       </c>
       <c r="E297" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>10</v>
@@ -9487,7 +9487,7 @@
         <v>9</v>
       </c>
       <c r="E298" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>15</v>
@@ -9507,7 +9507,7 @@
         <v>9</v>
       </c>
       <c r="E299" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>15</v>
@@ -9527,7 +9527,7 @@
         <v>9</v>
       </c>
       <c r="E300" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>18</v>
@@ -9547,7 +9547,7 @@
         <v>9</v>
       </c>
       <c r="E301" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>21</v>
@@ -9567,7 +9567,7 @@
         <v>9</v>
       </c>
       <c r="E302" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>10</v>
@@ -9587,7 +9587,7 @@
         <v>9</v>
       </c>
       <c r="E303" s="2">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>15</v>
@@ -9607,7 +9607,7 @@
         <v>9</v>
       </c>
       <c r="E304" s="2">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>15</v>
@@ -9627,7 +9627,7 @@
         <v>9</v>
       </c>
       <c r="E305" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>18</v>
@@ -9647,7 +9647,7 @@
         <v>9</v>
       </c>
       <c r="E306" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>21</v>
@@ -9667,7 +9667,7 @@
         <v>9</v>
       </c>
       <c r="E307" s="2">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>10</v>
@@ -9687,7 +9687,7 @@
         <v>9</v>
       </c>
       <c r="E308" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>15</v>
@@ -9707,7 +9707,7 @@
         <v>9</v>
       </c>
       <c r="E309" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>15</v>
@@ -9727,7 +9727,7 @@
         <v>9</v>
       </c>
       <c r="E310" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>18</v>
@@ -9747,7 +9747,7 @@
         <v>9</v>
       </c>
       <c r="E311" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>21</v>
@@ -9767,7 +9767,7 @@
         <v>9</v>
       </c>
       <c r="E312" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>10</v>
@@ -9787,7 +9787,7 @@
         <v>9</v>
       </c>
       <c r="E313" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>15</v>
@@ -9807,7 +9807,7 @@
         <v>9</v>
       </c>
       <c r="E314" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>15</v>
@@ -9827,7 +9827,7 @@
         <v>9</v>
       </c>
       <c r="E315" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>18</v>
@@ -9847,7 +9847,7 @@
         <v>9</v>
       </c>
       <c r="E316" s="2">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>21</v>
@@ -9867,7 +9867,7 @@
         <v>9</v>
       </c>
       <c r="E317" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>10</v>
@@ -9887,7 +9887,7 @@
         <v>9</v>
       </c>
       <c r="E318" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>15</v>
@@ -9907,7 +9907,7 @@
         <v>9</v>
       </c>
       <c r="E319" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>15</v>
@@ -9927,7 +9927,7 @@
         <v>9</v>
       </c>
       <c r="E320" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>18</v>
@@ -9947,7 +9947,7 @@
         <v>9</v>
       </c>
       <c r="E321" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>21</v>
@@ -9967,7 +9967,7 @@
         <v>9</v>
       </c>
       <c r="E322" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>10</v>
@@ -9987,7 +9987,7 @@
         <v>9</v>
       </c>
       <c r="E323" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>15</v>
@@ -10007,7 +10007,7 @@
         <v>9</v>
       </c>
       <c r="E324" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>15</v>
@@ -10027,7 +10027,7 @@
         <v>9</v>
       </c>
       <c r="E325" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>18</v>
@@ -10047,7 +10047,7 @@
         <v>9</v>
       </c>
       <c r="E326" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>21</v>
@@ -10067,7 +10067,7 @@
         <v>9</v>
       </c>
       <c r="E327" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>10</v>
@@ -10087,7 +10087,7 @@
         <v>9</v>
       </c>
       <c r="E328" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>15</v>
@@ -10107,7 +10107,7 @@
         <v>9</v>
       </c>
       <c r="E329" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>15</v>
@@ -10127,7 +10127,7 @@
         <v>9</v>
       </c>
       <c r="E330" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>18</v>
@@ -10147,7 +10147,7 @@
         <v>9</v>
       </c>
       <c r="E331" s="2">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>21</v>
@@ -10167,7 +10167,7 @@
         <v>9</v>
       </c>
       <c r="E332" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>10</v>
@@ -10187,7 +10187,7 @@
         <v>9</v>
       </c>
       <c r="E333" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>15</v>
@@ -10207,7 +10207,7 @@
         <v>9</v>
       </c>
       <c r="E334" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>15</v>
@@ -10227,7 +10227,7 @@
         <v>9</v>
       </c>
       <c r="E335" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>18</v>
@@ -10247,7 +10247,7 @@
         <v>9</v>
       </c>
       <c r="E336" s="2">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>21</v>
@@ -10267,7 +10267,7 @@
         <v>9</v>
       </c>
       <c r="E337" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F337" s="2" t="s">
         <v>10</v>
@@ -10287,7 +10287,7 @@
         <v>9</v>
       </c>
       <c r="E338" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F338" s="2" t="s">
         <v>15</v>
@@ -10327,7 +10327,7 @@
         <v>9</v>
       </c>
       <c r="E340" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>18</v>
@@ -10347,7 +10347,7 @@
         <v>9</v>
       </c>
       <c r="E341" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>21</v>
@@ -10367,7 +10367,7 @@
         <v>9</v>
       </c>
       <c r="E342" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>10</v>
@@ -10387,7 +10387,7 @@
         <v>9</v>
       </c>
       <c r="E343" s="2">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F343" s="2" t="s">
         <v>15</v>
@@ -10407,7 +10407,7 @@
         <v>9</v>
       </c>
       <c r="E344" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>15</v>
@@ -10427,7 +10427,7 @@
         <v>9</v>
       </c>
       <c r="E345" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>18</v>
@@ -10447,7 +10447,7 @@
         <v>9</v>
       </c>
       <c r="E346" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>21</v>
@@ -10467,7 +10467,7 @@
         <v>9</v>
       </c>
       <c r="E347" s="2">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>10</v>
@@ -10487,7 +10487,7 @@
         <v>9</v>
       </c>
       <c r="E348" s="2">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>15</v>
@@ -10527,7 +10527,7 @@
         <v>9</v>
       </c>
       <c r="E350" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F350" s="2" t="s">
         <v>18</v>
@@ -10547,7 +10547,7 @@
         <v>9</v>
       </c>
       <c r="E351" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F351" s="2" t="s">
         <v>21</v>
@@ -10567,7 +10567,7 @@
         <v>9</v>
       </c>
       <c r="E352" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>10</v>
@@ -10587,7 +10587,7 @@
         <v>9</v>
       </c>
       <c r="E353" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>15</v>
@@ -10607,7 +10607,7 @@
         <v>9</v>
       </c>
       <c r="E354" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>15</v>
@@ -10627,7 +10627,7 @@
         <v>9</v>
       </c>
       <c r="E355" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F355" s="2" t="s">
         <v>18</v>
@@ -10647,7 +10647,7 @@
         <v>9</v>
       </c>
       <c r="E356" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F356" s="2" t="s">
         <v>21</v>
@@ -10667,7 +10667,7 @@
         <v>9</v>
       </c>
       <c r="E357" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F357" s="2" t="s">
         <v>10</v>
@@ -10687,7 +10687,7 @@
         <v>9</v>
       </c>
       <c r="E358" s="2">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>15</v>
@@ -10707,7 +10707,7 @@
         <v>9</v>
       </c>
       <c r="E359" s="2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F359" s="2" t="s">
         <v>15</v>
@@ -10727,7 +10727,7 @@
         <v>9</v>
       </c>
       <c r="E360" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>18</v>
@@ -10747,7 +10747,7 @@
         <v>9</v>
       </c>
       <c r="E361" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>21</v>
@@ -10767,7 +10767,7 @@
         <v>9</v>
       </c>
       <c r="E362" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F362" s="2" t="s">
         <v>10</v>
@@ -10787,7 +10787,7 @@
         <v>9</v>
       </c>
       <c r="E363" s="2">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F363" s="2" t="s">
         <v>15</v>
@@ -10807,7 +10807,7 @@
         <v>9</v>
       </c>
       <c r="E364" s="2">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F364" s="2" t="s">
         <v>15</v>
@@ -10827,7 +10827,7 @@
         <v>9</v>
       </c>
       <c r="E365" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F365" s="2" t="s">
         <v>18</v>
@@ -10847,7 +10847,7 @@
         <v>9</v>
       </c>
       <c r="E366" s="2">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>21</v>
@@ -10867,7 +10867,7 @@
         <v>9</v>
       </c>
       <c r="E367" s="2">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F367" s="2" t="s">
         <v>10</v>
@@ -10887,7 +10887,7 @@
         <v>9</v>
       </c>
       <c r="E368" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F368" s="2" t="s">
         <v>15</v>
@@ -10907,7 +10907,7 @@
         <v>9</v>
       </c>
       <c r="E369" s="2">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F369" s="2" t="s">
         <v>15</v>
@@ -10927,7 +10927,7 @@
         <v>9</v>
       </c>
       <c r="E370" s="2">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F370" s="2" t="s">
         <v>18</v>
@@ -10947,7 +10947,7 @@
         <v>9</v>
       </c>
       <c r="E371" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F371" s="2" t="s">
         <v>21</v>
@@ -10967,7 +10967,7 @@
         <v>9</v>
       </c>
       <c r="E372" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F372" s="2" t="s">
         <v>10</v>
@@ -10987,7 +10987,7 @@
         <v>9</v>
       </c>
       <c r="E373" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F373" s="2" t="s">
         <v>15</v>
@@ -11007,7 +11007,7 @@
         <v>9</v>
       </c>
       <c r="E374" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F374" s="2" t="s">
         <v>15</v>
@@ -11027,7 +11027,7 @@
         <v>9</v>
       </c>
       <c r="E375" s="2">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F375" s="2" t="s">
         <v>18</v>
@@ -11047,7 +11047,7 @@
         <v>9</v>
       </c>
       <c r="E376" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>21</v>
@@ -11067,7 +11067,7 @@
         <v>9</v>
       </c>
       <c r="E377" s="2">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F377" s="2" t="s">
         <v>10</v>
@@ -11087,7 +11087,7 @@
         <v>9</v>
       </c>
       <c r="E378" s="2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>15</v>
@@ -11107,7 +11107,7 @@
         <v>9</v>
       </c>
       <c r="E379" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F379" s="2" t="s">
         <v>15</v>
@@ -11127,7 +11127,7 @@
         <v>9</v>
       </c>
       <c r="E380" s="2">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F380" s="2" t="s">
         <v>18</v>
@@ -11147,7 +11147,7 @@
         <v>9</v>
       </c>
       <c r="E381" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F381" s="2" t="s">
         <v>21</v>
@@ -11167,7 +11167,7 @@
         <v>9</v>
       </c>
       <c r="E382" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>10</v>
@@ -11187,7 +11187,7 @@
         <v>9</v>
       </c>
       <c r="E383" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F383" s="2" t="s">
         <v>15</v>
@@ -11207,7 +11207,7 @@
         <v>9</v>
       </c>
       <c r="E384" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F384" s="2" t="s">
         <v>15</v>
@@ -11227,7 +11227,7 @@
         <v>9</v>
       </c>
       <c r="E385" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F385" s="2" t="s">
         <v>18</v>
@@ -11247,7 +11247,7 @@
         <v>9</v>
       </c>
       <c r="E386" s="2">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="F386" s="2" t="s">
         <v>21</v>
@@ -11267,7 +11267,7 @@
         <v>9</v>
       </c>
       <c r="E387" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F387" s="2" t="s">
         <v>10</v>
@@ -11287,7 +11287,7 @@
         <v>9</v>
       </c>
       <c r="E388" s="2">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F388" s="2" t="s">
         <v>15</v>
@@ -11307,7 +11307,7 @@
         <v>9</v>
       </c>
       <c r="E389" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F389" s="2" t="s">
         <v>15</v>
@@ -11327,7 +11327,7 @@
         <v>9</v>
       </c>
       <c r="E390" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F390" s="2" t="s">
         <v>18</v>
@@ -11347,7 +11347,7 @@
         <v>9</v>
       </c>
       <c r="E391" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F391" s="2" t="s">
         <v>21</v>
@@ -11367,7 +11367,7 @@
         <v>9</v>
       </c>
       <c r="E392" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F392" s="2" t="s">
         <v>10</v>
@@ -11387,7 +11387,7 @@
         <v>9</v>
       </c>
       <c r="E393" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F393" s="2" t="s">
         <v>15</v>
@@ -11407,7 +11407,7 @@
         <v>9</v>
       </c>
       <c r="E394" s="2">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>15</v>
@@ -11427,7 +11427,7 @@
         <v>9</v>
       </c>
       <c r="E395" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F395" s="2" t="s">
         <v>18</v>
@@ -11447,7 +11447,7 @@
         <v>9</v>
       </c>
       <c r="E396" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F396" s="2" t="s">
         <v>21</v>
@@ -11467,7 +11467,7 @@
         <v>9</v>
       </c>
       <c r="E397" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F397" s="2" t="s">
         <v>10</v>
@@ -11487,7 +11487,7 @@
         <v>9</v>
       </c>
       <c r="E398" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>15</v>
@@ -11507,7 +11507,7 @@
         <v>9</v>
       </c>
       <c r="E399" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F399" s="2" t="s">
         <v>15</v>
@@ -11527,7 +11527,7 @@
         <v>9</v>
       </c>
       <c r="E400" s="2">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F400" s="2" t="s">
         <v>18</v>
@@ -11547,7 +11547,7 @@
         <v>9</v>
       </c>
       <c r="E401" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F401" s="2" t="s">
         <v>21</v>
@@ -11567,7 +11567,7 @@
         <v>9</v>
       </c>
       <c r="E402" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F402" s="2" t="s">
         <v>10</v>
@@ -11587,7 +11587,7 @@
         <v>9</v>
       </c>
       <c r="E403" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F403" s="2" t="s">
         <v>15</v>
@@ -11607,7 +11607,7 @@
         <v>9</v>
       </c>
       <c r="E404" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F404" s="2" t="s">
         <v>15</v>
@@ -11627,7 +11627,7 @@
         <v>9</v>
       </c>
       <c r="E405" s="2">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F405" s="2" t="s">
         <v>18</v>
@@ -11647,7 +11647,7 @@
         <v>9</v>
       </c>
       <c r="E406" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F406" s="2" t="s">
         <v>21</v>
@@ -11667,7 +11667,7 @@
         <v>9</v>
       </c>
       <c r="E407" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>10</v>
@@ -11687,7 +11687,7 @@
         <v>9</v>
       </c>
       <c r="E408" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F408" s="2" t="s">
         <v>15</v>
@@ -11707,7 +11707,7 @@
         <v>9</v>
       </c>
       <c r="E409" s="2">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F409" s="2" t="s">
         <v>15</v>
@@ -11727,7 +11727,7 @@
         <v>9</v>
       </c>
       <c r="E410" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F410" s="2" t="s">
         <v>18</v>
@@ -11747,7 +11747,7 @@
         <v>9</v>
       </c>
       <c r="E411" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F411" s="2" t="s">
         <v>21</v>
@@ -11767,7 +11767,7 @@
         <v>9</v>
       </c>
       <c r="E412" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F412" s="2" t="s">
         <v>10</v>
@@ -11787,7 +11787,7 @@
         <v>9</v>
       </c>
       <c r="E413" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F413" s="2" t="s">
         <v>15</v>
@@ -11807,7 +11807,7 @@
         <v>9</v>
       </c>
       <c r="E414" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F414" s="2" t="s">
         <v>15</v>
@@ -11827,7 +11827,7 @@
         <v>9</v>
       </c>
       <c r="E415" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F415" s="2" t="s">
         <v>18</v>
@@ -11847,7 +11847,7 @@
         <v>9</v>
       </c>
       <c r="E416" s="2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F416" s="2" t="s">
         <v>21</v>
@@ -11867,7 +11867,7 @@
         <v>9</v>
       </c>
       <c r="E417" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F417" s="2" t="s">
         <v>10</v>
@@ -11887,7 +11887,7 @@
         <v>9</v>
       </c>
       <c r="E418" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F418" s="2" t="s">
         <v>15</v>
@@ -11907,7 +11907,7 @@
         <v>9</v>
       </c>
       <c r="E419" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F419" s="2" t="s">
         <v>15</v>
@@ -11927,7 +11927,7 @@
         <v>9</v>
       </c>
       <c r="E420" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>18</v>
@@ -11967,7 +11967,7 @@
         <v>9</v>
       </c>
       <c r="E422" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F422" s="2" t="s">
         <v>10</v>
@@ -11987,7 +11987,7 @@
         <v>9</v>
       </c>
       <c r="E423" s="2">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="F423" s="2" t="s">
         <v>15</v>
@@ -12007,7 +12007,7 @@
         <v>9</v>
       </c>
       <c r="E424" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F424" s="2" t="s">
         <v>15</v>
@@ -12027,7 +12027,7 @@
         <v>9</v>
       </c>
       <c r="E425" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F425" s="2" t="s">
         <v>18</v>
@@ -12047,7 +12047,7 @@
         <v>9</v>
       </c>
       <c r="E426" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F426" s="2" t="s">
         <v>21</v>
@@ -12067,7 +12067,7 @@
         <v>9</v>
       </c>
       <c r="E427" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F427" s="2" t="s">
         <v>10</v>
@@ -12087,7 +12087,7 @@
         <v>9</v>
       </c>
       <c r="E428" s="2">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F428" s="2" t="s">
         <v>15</v>
@@ -12107,7 +12107,7 @@
         <v>9</v>
       </c>
       <c r="E429" s="2">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F429" s="2" t="s">
         <v>15</v>
@@ -12127,7 +12127,7 @@
         <v>9</v>
       </c>
       <c r="E430" s="2">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F430" s="2" t="s">
         <v>18</v>
@@ -12147,7 +12147,7 @@
         <v>9</v>
       </c>
       <c r="E431" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F431" s="2" t="s">
         <v>21</v>
@@ -12167,7 +12167,7 @@
         <v>9</v>
       </c>
       <c r="E432" s="2">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F432" s="2" t="s">
         <v>10</v>
@@ -12187,7 +12187,7 @@
         <v>9</v>
       </c>
       <c r="E433" s="2">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F433" s="2" t="s">
         <v>15</v>
@@ -12207,7 +12207,7 @@
         <v>9</v>
       </c>
       <c r="E434" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>15</v>
@@ -12227,7 +12227,7 @@
         <v>9</v>
       </c>
       <c r="E435" s="2">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="F435" s="2" t="s">
         <v>18</v>
@@ -12267,7 +12267,7 @@
         <v>9</v>
       </c>
       <c r="E437" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F437" s="2" t="s">
         <v>10</v>
@@ -12287,7 +12287,7 @@
         <v>9</v>
       </c>
       <c r="E438" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F438" s="2" t="s">
         <v>15</v>
@@ -12307,7 +12307,7 @@
         <v>9</v>
       </c>
       <c r="E439" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F439" s="2" t="s">
         <v>15</v>
@@ -12327,7 +12327,7 @@
         <v>9</v>
       </c>
       <c r="E440" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F440" s="2" t="s">
         <v>18</v>
@@ -12347,7 +12347,7 @@
         <v>9</v>
       </c>
       <c r="E441" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F441" s="2" t="s">
         <v>21</v>
@@ -12367,7 +12367,7 @@
         <v>9</v>
       </c>
       <c r="E442" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F442" s="2" t="s">
         <v>10</v>
@@ -12387,7 +12387,7 @@
         <v>9</v>
       </c>
       <c r="E443" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F443" s="2" t="s">
         <v>15</v>
@@ -12407,7 +12407,7 @@
         <v>9</v>
       </c>
       <c r="E444" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F444" s="2" t="s">
         <v>15</v>
@@ -12427,7 +12427,7 @@
         <v>9</v>
       </c>
       <c r="E445" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F445" s="2" t="s">
         <v>18</v>
@@ -12447,7 +12447,7 @@
         <v>9</v>
       </c>
       <c r="E446" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F446" s="2" t="s">
         <v>21</v>
@@ -12467,7 +12467,7 @@
         <v>9</v>
       </c>
       <c r="E447" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F447" s="2" t="s">
         <v>10</v>
@@ -12487,7 +12487,7 @@
         <v>9</v>
       </c>
       <c r="E448" s="2">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F448" s="2" t="s">
         <v>15</v>
@@ -12507,7 +12507,7 @@
         <v>9</v>
       </c>
       <c r="E449" s="2">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F449" s="2" t="s">
         <v>15</v>
@@ -12527,7 +12527,7 @@
         <v>9</v>
       </c>
       <c r="E450" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F450" s="2" t="s">
         <v>18</v>
@@ -12547,7 +12547,7 @@
         <v>9</v>
       </c>
       <c r="E451" s="2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F451" s="2" t="s">
         <v>21</v>
@@ -12567,7 +12567,7 @@
         <v>9</v>
       </c>
       <c r="E452" s="2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F452" s="2" t="s">
         <v>10</v>
@@ -12587,7 +12587,7 @@
         <v>9</v>
       </c>
       <c r="E453" s="2">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F453" s="2" t="s">
         <v>15</v>
@@ -12607,7 +12607,7 @@
         <v>9</v>
       </c>
       <c r="E454" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F454" s="2" t="s">
         <v>15</v>
@@ -12627,7 +12627,7 @@
         <v>9</v>
       </c>
       <c r="E455" s="2">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F455" s="2" t="s">
         <v>18</v>
@@ -12647,7 +12647,7 @@
         <v>9</v>
       </c>
       <c r="E456" s="2">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F456" s="2" t="s">
         <v>21</v>
@@ -12667,7 +12667,7 @@
         <v>9</v>
       </c>
       <c r="E457" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F457" s="2" t="s">
         <v>10</v>
@@ -12687,7 +12687,7 @@
         <v>9</v>
       </c>
       <c r="E458" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F458" s="2" t="s">
         <v>15</v>
@@ -12707,7 +12707,7 @@
         <v>9</v>
       </c>
       <c r="E459" s="2">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F459" s="2" t="s">
         <v>15</v>
@@ -12727,7 +12727,7 @@
         <v>9</v>
       </c>
       <c r="E460" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F460" s="2" t="s">
         <v>18</v>
@@ -12747,7 +12747,7 @@
         <v>9</v>
       </c>
       <c r="E461" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F461" s="2" t="s">
         <v>21</v>
@@ -12767,7 +12767,7 @@
         <v>9</v>
       </c>
       <c r="E462" s="2">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F462" s="2" t="s">
         <v>10</v>
@@ -12787,7 +12787,7 @@
         <v>9</v>
       </c>
       <c r="E463" s="2">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F463" s="2" t="s">
         <v>15</v>
@@ -12807,7 +12807,7 @@
         <v>9</v>
       </c>
       <c r="E464" s="2">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>15</v>
@@ -12827,7 +12827,7 @@
         <v>9</v>
       </c>
       <c r="E465" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>18</v>
@@ -12847,7 +12847,7 @@
         <v>9</v>
       </c>
       <c r="E466" s="2">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F466" s="2" t="s">
         <v>21</v>
@@ -12867,7 +12867,7 @@
         <v>9</v>
       </c>
       <c r="E467" s="2">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>10</v>
@@ -12887,7 +12887,7 @@
         <v>9</v>
       </c>
       <c r="E468" s="2">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F468" s="2" t="s">
         <v>15</v>
@@ -12907,7 +12907,7 @@
         <v>9</v>
       </c>
       <c r="E469" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F469" s="2" t="s">
         <v>15</v>
@@ -12927,7 +12927,7 @@
         <v>9</v>
       </c>
       <c r="E470" s="2">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F470" s="2" t="s">
         <v>18</v>
@@ -12947,7 +12947,7 @@
         <v>9</v>
       </c>
       <c r="E471" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F471" s="2" t="s">
         <v>21</v>
@@ -13006,7 +13006,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>10</v>
@@ -13026,7 +13026,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -13046,7 +13046,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>15</v>
@@ -13066,7 +13066,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>18</v>
@@ -13086,7 +13086,7 @@
         <v>9</v>
       </c>
       <c r="E6" s="2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>21</v>
@@ -13106,7 +13106,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="2">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
@@ -13126,7 +13126,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="2">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
@@ -13146,7 +13146,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -13166,7 +13166,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
@@ -13186,7 +13186,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>21</v>
@@ -13206,7 +13206,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>10</v>
@@ -13226,7 +13226,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="2">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>15</v>
@@ -13246,7 +13246,7 @@
         <v>9</v>
       </c>
       <c r="E14" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>15</v>
@@ -13266,7 +13266,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="2">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
@@ -13286,7 +13286,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>21</v>
@@ -13306,7 +13306,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
@@ -13326,7 +13326,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>15</v>
@@ -13346,7 +13346,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>15</v>
@@ -13366,7 +13366,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
@@ -13386,7 +13386,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="2">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>21</v>
@@ -13406,7 +13406,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="2">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -13426,7 +13426,7 @@
         <v>9</v>
       </c>
       <c r="E23" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>15</v>
@@ -13446,7 +13446,7 @@
         <v>9</v>
       </c>
       <c r="E24" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>15</v>
@@ -13466,7 +13466,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>18</v>
@@ -13486,7 +13486,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>21</v>
@@ -13506,7 +13506,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -13526,7 +13526,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>15</v>
@@ -13546,7 +13546,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>15</v>
@@ -13566,7 +13566,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
@@ -13586,7 +13586,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="2">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>21</v>
@@ -13606,7 +13606,7 @@
         <v>9</v>
       </c>
       <c r="E32" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -13626,7 +13626,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>15</v>
@@ -13646,7 +13646,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="2">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>15</v>
@@ -13666,7 +13666,7 @@
         <v>9</v>
       </c>
       <c r="E35" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>18</v>
@@ -13686,7 +13686,7 @@
         <v>9</v>
       </c>
       <c r="E36" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>21</v>
@@ -13706,7 +13706,7 @@
         <v>9</v>
       </c>
       <c r="E37" s="2">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>10</v>
@@ -13726,7 +13726,7 @@
         <v>9</v>
       </c>
       <c r="E38" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>15</v>
@@ -13746,7 +13746,7 @@
         <v>9</v>
       </c>
       <c r="E39" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>15</v>
@@ -13766,7 +13766,7 @@
         <v>9</v>
       </c>
       <c r="E40" s="2">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>18</v>
@@ -13786,7 +13786,7 @@
         <v>9</v>
       </c>
       <c r="E41" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>21</v>
@@ -13806,7 +13806,7 @@
         <v>9</v>
       </c>
       <c r="E42" s="2">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -13826,7 +13826,7 @@
         <v>9</v>
       </c>
       <c r="E43" s="2">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>15</v>
@@ -13846,7 +13846,7 @@
         <v>9</v>
       </c>
       <c r="E44" s="2">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>15</v>
@@ -13866,7 +13866,7 @@
         <v>9</v>
       </c>
       <c r="E45" s="2">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>18</v>
@@ -13886,7 +13886,7 @@
         <v>9</v>
       </c>
       <c r="E46" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>21</v>
@@ -13906,7 +13906,7 @@
         <v>9</v>
       </c>
       <c r="E47" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -13926,7 +13926,7 @@
         <v>9</v>
       </c>
       <c r="E48" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>15</v>
@@ -13946,7 +13946,7 @@
         <v>9</v>
       </c>
       <c r="E49" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>15</v>
@@ -13966,7 +13966,7 @@
         <v>9</v>
       </c>
       <c r="E50" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>18</v>
@@ -13986,7 +13986,7 @@
         <v>9</v>
       </c>
       <c r="E51" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>21</v>
@@ -14006,7 +14006,7 @@
         <v>9</v>
       </c>
       <c r="E52" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -14026,7 +14026,7 @@
         <v>9</v>
       </c>
       <c r="E53" s="2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>15</v>
@@ -14046,7 +14046,7 @@
         <v>9</v>
       </c>
       <c r="E54" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>15</v>
@@ -14066,7 +14066,7 @@
         <v>9</v>
       </c>
       <c r="E55" s="2">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>18</v>
@@ -14086,7 +14086,7 @@
         <v>9</v>
       </c>
       <c r="E56" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>21</v>
@@ -14106,7 +14106,7 @@
         <v>9</v>
       </c>
       <c r="E57" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -14126,7 +14126,7 @@
         <v>9</v>
       </c>
       <c r="E58" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>15</v>
@@ -14146,7 +14146,7 @@
         <v>9</v>
       </c>
       <c r="E59" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>15</v>
@@ -14166,7 +14166,7 @@
         <v>9</v>
       </c>
       <c r="E60" s="2">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>18</v>
@@ -14186,7 +14186,7 @@
         <v>9</v>
       </c>
       <c r="E61" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>21</v>
@@ -14206,7 +14206,7 @@
         <v>9</v>
       </c>
       <c r="E62" s="2">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -14226,7 +14226,7 @@
         <v>9</v>
       </c>
       <c r="E63" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>15</v>
@@ -14246,7 +14246,7 @@
         <v>9</v>
       </c>
       <c r="E64" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>15</v>
@@ -14266,7 +14266,7 @@
         <v>9</v>
       </c>
       <c r="E65" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>18</v>
@@ -14306,7 +14306,7 @@
         <v>9</v>
       </c>
       <c r="E67" s="2">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -14326,7 +14326,7 @@
         <v>9</v>
       </c>
       <c r="E68" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>15</v>
@@ -14346,7 +14346,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>15</v>
@@ -14366,7 +14366,7 @@
         <v>9</v>
       </c>
       <c r="E70" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>18</v>
@@ -14386,7 +14386,7 @@
         <v>9</v>
       </c>
       <c r="E71" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>21</v>
@@ -14406,7 +14406,7 @@
         <v>9</v>
       </c>
       <c r="E72" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -14426,7 +14426,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="2">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>15</v>
@@ -14446,7 +14446,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>15</v>
@@ -14466,7 +14466,7 @@
         <v>9</v>
       </c>
       <c r="E75" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>18</v>
@@ -14486,7 +14486,7 @@
         <v>9</v>
       </c>
       <c r="E76" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>21</v>
@@ -14506,7 +14506,7 @@
         <v>9</v>
       </c>
       <c r="E77" s="2">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -14526,7 +14526,7 @@
         <v>9</v>
       </c>
       <c r="E78" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>15</v>
@@ -14546,7 +14546,7 @@
         <v>9</v>
       </c>
       <c r="E79" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>15</v>
@@ -14566,7 +14566,7 @@
         <v>9</v>
       </c>
       <c r="E80" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>18</v>
@@ -14586,7 +14586,7 @@
         <v>9</v>
       </c>
       <c r="E81" s="2">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>21</v>
@@ -14606,7 +14606,7 @@
         <v>9</v>
       </c>
       <c r="E82" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -14626,7 +14626,7 @@
         <v>9</v>
       </c>
       <c r="E83" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>15</v>
@@ -14646,7 +14646,7 @@
         <v>9</v>
       </c>
       <c r="E84" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>15</v>
@@ -14666,7 +14666,7 @@
         <v>9</v>
       </c>
       <c r="E85" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>18</v>
@@ -14686,7 +14686,7 @@
         <v>9</v>
       </c>
       <c r="E86" s="2">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>21</v>
@@ -14706,7 +14706,7 @@
         <v>9</v>
       </c>
       <c r="E87" s="2">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -14726,7 +14726,7 @@
         <v>9</v>
       </c>
       <c r="E88" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>15</v>
@@ -14746,7 +14746,7 @@
         <v>9</v>
       </c>
       <c r="E89" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>15</v>
@@ -14766,7 +14766,7 @@
         <v>9</v>
       </c>
       <c r="E90" s="2">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>18</v>
@@ -14786,7 +14786,7 @@
         <v>9</v>
       </c>
       <c r="E91" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>21</v>
@@ -14806,7 +14806,7 @@
         <v>9</v>
       </c>
       <c r="E92" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -14826,7 +14826,7 @@
         <v>9</v>
       </c>
       <c r="E93" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>15</v>
@@ -14846,7 +14846,7 @@
         <v>9</v>
       </c>
       <c r="E94" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>15</v>
@@ -14866,7 +14866,7 @@
         <v>9</v>
       </c>
       <c r="E95" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>18</v>
@@ -14886,7 +14886,7 @@
         <v>9</v>
       </c>
       <c r="E96" s="2">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>21</v>
@@ -14906,7 +14906,7 @@
         <v>9</v>
       </c>
       <c r="E97" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -14946,7 +14946,7 @@
         <v>9</v>
       </c>
       <c r="E99" s="2">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>15</v>
@@ -14966,7 +14966,7 @@
         <v>9</v>
       </c>
       <c r="E100" s="2">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>18</v>
@@ -14986,7 +14986,7 @@
         <v>9</v>
       </c>
       <c r="E101" s="2">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>21</v>
@@ -15006,7 +15006,7 @@
         <v>9</v>
       </c>
       <c r="E102" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -15026,7 +15026,7 @@
         <v>9</v>
       </c>
       <c r="E103" s="2">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>15</v>
@@ -15046,7 +15046,7 @@
         <v>9</v>
       </c>
       <c r="E104" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>15</v>
@@ -15066,7 +15066,7 @@
         <v>9</v>
       </c>
       <c r="E105" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>18</v>
@@ -15086,7 +15086,7 @@
         <v>9</v>
       </c>
       <c r="E106" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>21</v>
@@ -15106,7 +15106,7 @@
         <v>9</v>
       </c>
       <c r="E107" s="2">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -15126,7 +15126,7 @@
         <v>9</v>
       </c>
       <c r="E108" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>15</v>
@@ -15146,7 +15146,7 @@
         <v>9</v>
       </c>
       <c r="E109" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>15</v>
@@ -15166,7 +15166,7 @@
         <v>9</v>
       </c>
       <c r="E110" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>18</v>
@@ -15186,7 +15186,7 @@
         <v>9</v>
       </c>
       <c r="E111" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>21</v>
@@ -15206,7 +15206,7 @@
         <v>9</v>
       </c>
       <c r="E112" s="2">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -15226,7 +15226,7 @@
         <v>9</v>
       </c>
       <c r="E113" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>15</v>
@@ -15246,7 +15246,7 @@
         <v>9</v>
       </c>
       <c r="E114" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>15</v>
@@ -15266,7 +15266,7 @@
         <v>9</v>
       </c>
       <c r="E115" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>18</v>
@@ -15286,7 +15286,7 @@
         <v>9</v>
       </c>
       <c r="E116" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>21</v>
@@ -15306,7 +15306,7 @@
         <v>9</v>
       </c>
       <c r="E117" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -15326,7 +15326,7 @@
         <v>9</v>
       </c>
       <c r="E118" s="2">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>15</v>
@@ -15346,7 +15346,7 @@
         <v>9</v>
       </c>
       <c r="E119" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>15</v>
@@ -15366,7 +15366,7 @@
         <v>9</v>
       </c>
       <c r="E120" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>18</v>
@@ -15386,7 +15386,7 @@
         <v>9</v>
       </c>
       <c r="E121" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>21</v>
@@ -15406,7 +15406,7 @@
         <v>9</v>
       </c>
       <c r="E122" s="2">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -15426,7 +15426,7 @@
         <v>9</v>
       </c>
       <c r="E123" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>15</v>
@@ -15446,7 +15446,7 @@
         <v>9</v>
       </c>
       <c r="E124" s="2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>15</v>
@@ -15466,7 +15466,7 @@
         <v>9</v>
       </c>
       <c r="E125" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>18</v>
@@ -15486,7 +15486,7 @@
         <v>9</v>
       </c>
       <c r="E126" s="2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>21</v>
@@ -15506,7 +15506,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -15526,7 +15526,7 @@
         <v>9</v>
       </c>
       <c r="E128" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>15</v>
@@ -15546,7 +15546,7 @@
         <v>9</v>
       </c>
       <c r="E129" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>15</v>
@@ -15566,7 +15566,7 @@
         <v>9</v>
       </c>
       <c r="E130" s="2">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>18</v>
@@ -15586,7 +15586,7 @@
         <v>9</v>
       </c>
       <c r="E131" s="2">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>21</v>
@@ -15626,7 +15626,7 @@
         <v>9</v>
       </c>
       <c r="E133" s="2">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>15</v>
@@ -15646,7 +15646,7 @@
         <v>9</v>
       </c>
       <c r="E134" s="2">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>15</v>
@@ -15666,7 +15666,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="2">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>18</v>
@@ -15686,7 +15686,7 @@
         <v>9</v>
       </c>
       <c r="E136" s="2">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>21</v>
@@ -15706,7 +15706,7 @@
         <v>9</v>
       </c>
       <c r="E137" s="2">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
@@ -15726,7 +15726,7 @@
         <v>9</v>
       </c>
       <c r="E138" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>15</v>
@@ -15746,7 +15746,7 @@
         <v>9</v>
       </c>
       <c r="E139" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>15</v>
@@ -15766,7 +15766,7 @@
         <v>9</v>
       </c>
       <c r="E140" s="2">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>18</v>
@@ -15786,7 +15786,7 @@
         <v>9</v>
       </c>
       <c r="E141" s="2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>21</v>
@@ -15806,7 +15806,7 @@
         <v>9</v>
       </c>
       <c r="E142" s="2">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -15826,7 +15826,7 @@
         <v>9</v>
       </c>
       <c r="E143" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>15</v>
@@ -15846,7 +15846,7 @@
         <v>9</v>
       </c>
       <c r="E144" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>15</v>
@@ -15866,7 +15866,7 @@
         <v>9</v>
       </c>
       <c r="E145" s="2">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>18</v>
@@ -15886,7 +15886,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>21</v>
@@ -15906,7 +15906,7 @@
         <v>9</v>
       </c>
       <c r="E147" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
@@ -15926,7 +15926,7 @@
         <v>9</v>
       </c>
       <c r="E148" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>15</v>
@@ -15946,7 +15946,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>15</v>
@@ -15966,7 +15966,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="2">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>18</v>
@@ -15986,7 +15986,7 @@
         <v>9</v>
       </c>
       <c r="E151" s="2">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>21</v>
@@ -16006,7 +16006,7 @@
         <v>9</v>
       </c>
       <c r="E152" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
@@ -16026,7 +16026,7 @@
         <v>9</v>
       </c>
       <c r="E153" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>15</v>
@@ -16046,7 +16046,7 @@
         <v>9</v>
       </c>
       <c r="E154" s="2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>15</v>
@@ -16066,7 +16066,7 @@
         <v>9</v>
       </c>
       <c r="E155" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>18</v>
@@ -16086,7 +16086,7 @@
         <v>9</v>
       </c>
       <c r="E156" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>21</v>
@@ -16106,7 +16106,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>10</v>
@@ -16126,7 +16126,7 @@
         <v>9</v>
       </c>
       <c r="E158" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>15</v>
@@ -16146,7 +16146,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>15</v>
@@ -16166,7 +16166,7 @@
         <v>9</v>
       </c>
       <c r="E160" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>18</v>
@@ -16186,7 +16186,7 @@
         <v>9</v>
       </c>
       <c r="E161" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>21</v>
@@ -16206,7 +16206,7 @@
         <v>9</v>
       </c>
       <c r="E162" s="2">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>10</v>
@@ -16226,7 +16226,7 @@
         <v>9</v>
       </c>
       <c r="E163" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>15</v>
@@ -16246,7 +16246,7 @@
         <v>9</v>
       </c>
       <c r="E164" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>15</v>
@@ -16266,7 +16266,7 @@
         <v>9</v>
       </c>
       <c r="E165" s="2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>18</v>
@@ -16286,7 +16286,7 @@
         <v>9</v>
       </c>
       <c r="E166" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>21</v>
@@ -16306,7 +16306,7 @@
         <v>9</v>
       </c>
       <c r="E167" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>10</v>
@@ -16326,7 +16326,7 @@
         <v>9</v>
       </c>
       <c r="E168" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>15</v>
@@ -16346,7 +16346,7 @@
         <v>9</v>
       </c>
       <c r="E169" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>15</v>
@@ -16366,7 +16366,7 @@
         <v>9</v>
       </c>
       <c r="E170" s="2">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>18</v>
@@ -16386,7 +16386,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="2">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>21</v>
@@ -16406,7 +16406,7 @@
         <v>9</v>
       </c>
       <c r="E172" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
@@ -16426,7 +16426,7 @@
         <v>9</v>
       </c>
       <c r="E173" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>15</v>
@@ -16446,7 +16446,7 @@
         <v>9</v>
       </c>
       <c r="E174" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>15</v>
@@ -16466,7 +16466,7 @@
         <v>9</v>
       </c>
       <c r="E175" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>18</v>
@@ -16486,7 +16486,7 @@
         <v>9</v>
       </c>
       <c r="E176" s="2">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>21</v>
@@ -16506,7 +16506,7 @@
         <v>9</v>
       </c>
       <c r="E177" s="2">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>10</v>
@@ -16526,7 +16526,7 @@
         <v>9</v>
       </c>
       <c r="E178" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>15</v>
@@ -16546,7 +16546,7 @@
         <v>9</v>
       </c>
       <c r="E179" s="2">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>15</v>
@@ -16566,7 +16566,7 @@
         <v>9</v>
       </c>
       <c r="E180" s="2">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>18</v>
@@ -16586,7 +16586,7 @@
         <v>9</v>
       </c>
       <c r="E181" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>21</v>
@@ -16606,7 +16606,7 @@
         <v>9</v>
       </c>
       <c r="E182" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>10</v>
@@ -16626,7 +16626,7 @@
         <v>9</v>
       </c>
       <c r="E183" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>15</v>
@@ -16646,7 +16646,7 @@
         <v>9</v>
       </c>
       <c r="E184" s="2">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>15</v>
@@ -16666,7 +16666,7 @@
         <v>9</v>
       </c>
       <c r="E185" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>18</v>
@@ -16686,7 +16686,7 @@
         <v>9</v>
       </c>
       <c r="E186" s="2">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>21</v>
@@ -16706,7 +16706,7 @@
         <v>9</v>
       </c>
       <c r="E187" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>10</v>
@@ -16726,7 +16726,7 @@
         <v>9</v>
       </c>
       <c r="E188" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>15</v>
@@ -16746,7 +16746,7 @@
         <v>9</v>
       </c>
       <c r="E189" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>15</v>
@@ -16766,7 +16766,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="2">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>18</v>
@@ -16786,7 +16786,7 @@
         <v>9</v>
       </c>
       <c r="E191" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>21</v>
@@ -16806,7 +16806,7 @@
         <v>9</v>
       </c>
       <c r="E192" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>10</v>
@@ -16826,7 +16826,7 @@
         <v>9</v>
       </c>
       <c r="E193" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>15</v>
@@ -16846,7 +16846,7 @@
         <v>9</v>
       </c>
       <c r="E194" s="2">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>15</v>
@@ -16866,7 +16866,7 @@
         <v>9</v>
       </c>
       <c r="E195" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>18</v>
@@ -16886,7 +16886,7 @@
         <v>9</v>
       </c>
       <c r="E196" s="2">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>21</v>
@@ -16906,7 +16906,7 @@
         <v>9</v>
       </c>
       <c r="E197" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>10</v>
@@ -16926,7 +16926,7 @@
         <v>9</v>
       </c>
       <c r="E198" s="2">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>15</v>
@@ -16946,7 +16946,7 @@
         <v>9</v>
       </c>
       <c r="E199" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>15</v>
@@ -16966,7 +16966,7 @@
         <v>9</v>
       </c>
       <c r="E200" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>18</v>
@@ -16986,7 +16986,7 @@
         <v>9</v>
       </c>
       <c r="E201" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>21</v>
@@ -17006,7 +17006,7 @@
         <v>9</v>
       </c>
       <c r="E202" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>10</v>
@@ -17026,7 +17026,7 @@
         <v>9</v>
       </c>
       <c r="E203" s="2">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>15</v>
@@ -17046,7 +17046,7 @@
         <v>9</v>
       </c>
       <c r="E204" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>15</v>
@@ -17066,7 +17066,7 @@
         <v>9</v>
       </c>
       <c r="E205" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>18</v>
@@ -17086,7 +17086,7 @@
         <v>9</v>
       </c>
       <c r="E206" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>21</v>
@@ -17106,7 +17106,7 @@
         <v>9</v>
       </c>
       <c r="E207" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>10</v>
@@ -17126,7 +17126,7 @@
         <v>9</v>
       </c>
       <c r="E208" s="2">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>15</v>
@@ -17146,7 +17146,7 @@
         <v>9</v>
       </c>
       <c r="E209" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>15</v>
@@ -17166,7 +17166,7 @@
         <v>9</v>
       </c>
       <c r="E210" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>18</v>
@@ -17206,7 +17206,7 @@
         <v>9</v>
       </c>
       <c r="E212" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>10</v>
@@ -17226,7 +17226,7 @@
         <v>9</v>
       </c>
       <c r="E213" s="2">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>15</v>
@@ -17246,7 +17246,7 @@
         <v>9</v>
       </c>
       <c r="E214" s="2">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>15</v>
@@ -17266,7 +17266,7 @@
         <v>9</v>
       </c>
       <c r="E215" s="2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>18</v>
@@ -17286,7 +17286,7 @@
         <v>9</v>
       </c>
       <c r="E216" s="2">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>21</v>
@@ -17306,7 +17306,7 @@
         <v>9</v>
       </c>
       <c r="E217" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>10</v>
@@ -17326,7 +17326,7 @@
         <v>9</v>
       </c>
       <c r="E218" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>15</v>
@@ -17346,7 +17346,7 @@
         <v>9</v>
       </c>
       <c r="E219" s="2">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>15</v>
@@ -17366,7 +17366,7 @@
         <v>9</v>
       </c>
       <c r="E220" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>18</v>
@@ -17386,7 +17386,7 @@
         <v>9</v>
       </c>
       <c r="E221" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>21</v>
@@ -17406,7 +17406,7 @@
         <v>9</v>
       </c>
       <c r="E222" s="2">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>10</v>
@@ -17426,7 +17426,7 @@
         <v>9</v>
       </c>
       <c r="E223" s="2">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>15</v>
@@ -17446,7 +17446,7 @@
         <v>9</v>
       </c>
       <c r="E224" s="2">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>15</v>
@@ -17466,7 +17466,7 @@
         <v>9</v>
       </c>
       <c r="E225" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>18</v>
@@ -17486,7 +17486,7 @@
         <v>9</v>
       </c>
       <c r="E226" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>21</v>
@@ -17506,7 +17506,7 @@
         <v>9</v>
       </c>
       <c r="E227" s="2">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>10</v>
@@ -17526,7 +17526,7 @@
         <v>9</v>
       </c>
       <c r="E228" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>15</v>
@@ -17546,7 +17546,7 @@
         <v>9</v>
       </c>
       <c r="E229" s="2">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>15</v>
@@ -17566,7 +17566,7 @@
         <v>9</v>
       </c>
       <c r="E230" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>18</v>
@@ -17586,7 +17586,7 @@
         <v>9</v>
       </c>
       <c r="E231" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>21</v>
@@ -17606,7 +17606,7 @@
         <v>9</v>
       </c>
       <c r="E232" s="2">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>10</v>
@@ -17626,7 +17626,7 @@
         <v>9</v>
       </c>
       <c r="E233" s="2">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>15</v>
@@ -17646,7 +17646,7 @@
         <v>9</v>
       </c>
       <c r="E234" s="2">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>15</v>
@@ -17666,7 +17666,7 @@
         <v>9</v>
       </c>
       <c r="E235" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>18</v>
@@ -17686,7 +17686,7 @@
         <v>9</v>
       </c>
       <c r="E236" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>21</v>
@@ -17706,7 +17706,7 @@
         <v>9</v>
       </c>
       <c r="E237" s="2">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>10</v>
@@ -17726,7 +17726,7 @@
         <v>9</v>
       </c>
       <c r="E238" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>15</v>
@@ -17746,7 +17746,7 @@
         <v>9</v>
       </c>
       <c r="E239" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>15</v>
@@ -17766,7 +17766,7 @@
         <v>9</v>
       </c>
       <c r="E240" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>18</v>
@@ -17786,7 +17786,7 @@
         <v>9</v>
       </c>
       <c r="E241" s="2">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>21</v>
@@ -17806,7 +17806,7 @@
         <v>9</v>
       </c>
       <c r="E242" s="2">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>10</v>
@@ -17826,7 +17826,7 @@
         <v>9</v>
       </c>
       <c r="E243" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>15</v>
@@ -17846,7 +17846,7 @@
         <v>9</v>
       </c>
       <c r="E244" s="2">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>15</v>
@@ -17866,7 +17866,7 @@
         <v>9</v>
       </c>
       <c r="E245" s="2">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>18</v>
@@ -17886,7 +17886,7 @@
         <v>9</v>
       </c>
       <c r="E246" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>21</v>
@@ -17906,7 +17906,7 @@
         <v>9</v>
       </c>
       <c r="E247" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>10</v>
@@ -17926,7 +17926,7 @@
         <v>9</v>
       </c>
       <c r="E248" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>15</v>
@@ -17946,7 +17946,7 @@
         <v>9</v>
       </c>
       <c r="E249" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>15</v>
@@ -17966,7 +17966,7 @@
         <v>9</v>
       </c>
       <c r="E250" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>18</v>
@@ -17986,7 +17986,7 @@
         <v>9</v>
       </c>
       <c r="E251" s="2">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>21</v>
@@ -18006,7 +18006,7 @@
         <v>9</v>
       </c>
       <c r="E252" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>10</v>
@@ -18026,7 +18026,7 @@
         <v>9</v>
       </c>
       <c r="E253" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>15</v>
@@ -18046,7 +18046,7 @@
         <v>9</v>
       </c>
       <c r="E254" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>15</v>
@@ -18066,7 +18066,7 @@
         <v>9</v>
       </c>
       <c r="E255" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>18</v>
@@ -18086,7 +18086,7 @@
         <v>9</v>
       </c>
       <c r="E256" s="2">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>21</v>
@@ -18106,7 +18106,7 @@
         <v>9</v>
       </c>
       <c r="E257" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>10</v>
@@ -18126,7 +18126,7 @@
         <v>9</v>
       </c>
       <c r="E258" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>15</v>
@@ -18146,7 +18146,7 @@
         <v>9</v>
       </c>
       <c r="E259" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>15</v>
@@ -18166,7 +18166,7 @@
         <v>9</v>
       </c>
       <c r="E260" s="2">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>18</v>
@@ -18186,7 +18186,7 @@
         <v>9</v>
       </c>
       <c r="E261" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>21</v>
@@ -18206,7 +18206,7 @@
         <v>9</v>
       </c>
       <c r="E262" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>10</v>
@@ -18226,7 +18226,7 @@
         <v>9</v>
       </c>
       <c r="E263" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>15</v>
@@ -18246,7 +18246,7 @@
         <v>9</v>
       </c>
       <c r="E264" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>15</v>
@@ -18266,7 +18266,7 @@
         <v>9</v>
       </c>
       <c r="E265" s="2">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>18</v>
@@ -18286,7 +18286,7 @@
         <v>9</v>
       </c>
       <c r="E266" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>21</v>
@@ -18306,7 +18306,7 @@
         <v>9</v>
       </c>
       <c r="E267" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>10</v>
@@ -18326,7 +18326,7 @@
         <v>9</v>
       </c>
       <c r="E268" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>15</v>
@@ -18346,7 +18346,7 @@
         <v>9</v>
       </c>
       <c r="E269" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>15</v>
@@ -18366,7 +18366,7 @@
         <v>9</v>
       </c>
       <c r="E270" s="2">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>18</v>
@@ -18386,7 +18386,7 @@
         <v>9</v>
       </c>
       <c r="E271" s="2">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>21</v>
@@ -18406,7 +18406,7 @@
         <v>9</v>
       </c>
       <c r="E272" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>10</v>
@@ -18426,7 +18426,7 @@
         <v>9</v>
       </c>
       <c r="E273" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>15</v>
@@ -18446,7 +18446,7 @@
         <v>9</v>
       </c>
       <c r="E274" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>15</v>
@@ -18466,7 +18466,7 @@
         <v>9</v>
       </c>
       <c r="E275" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>18</v>
@@ -18486,7 +18486,7 @@
         <v>9</v>
       </c>
       <c r="E276" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>21</v>
@@ -18506,7 +18506,7 @@
         <v>9</v>
       </c>
       <c r="E277" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>10</v>
@@ -18526,7 +18526,7 @@
         <v>9</v>
       </c>
       <c r="E278" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>15</v>
@@ -18546,7 +18546,7 @@
         <v>9</v>
       </c>
       <c r="E279" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>15</v>
@@ -18566,7 +18566,7 @@
         <v>9</v>
       </c>
       <c r="E280" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>18</v>
@@ -18586,7 +18586,7 @@
         <v>9</v>
       </c>
       <c r="E281" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>21</v>
@@ -18626,7 +18626,7 @@
         <v>9</v>
       </c>
       <c r="E283" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>15</v>
@@ -18646,7 +18646,7 @@
         <v>9</v>
       </c>
       <c r="E284" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>15</v>
@@ -18666,7 +18666,7 @@
         <v>9</v>
       </c>
       <c r="E285" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>18</v>
@@ -18686,7 +18686,7 @@
         <v>9</v>
       </c>
       <c r="E286" s="2">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>21</v>
@@ -18706,7 +18706,7 @@
         <v>9</v>
       </c>
       <c r="E287" s="2">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>10</v>
@@ -18726,7 +18726,7 @@
         <v>9</v>
       </c>
       <c r="E288" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>15</v>
@@ -18746,7 +18746,7 @@
         <v>9</v>
       </c>
       <c r="E289" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>15</v>
@@ -18766,7 +18766,7 @@
         <v>9</v>
       </c>
       <c r="E290" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>18</v>
@@ -18786,7 +18786,7 @@
         <v>9</v>
       </c>
       <c r="E291" s="2">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>21</v>
@@ -18806,7 +18806,7 @@
         <v>9</v>
       </c>
       <c r="E292" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>10</v>
@@ -18826,7 +18826,7 @@
         <v>9</v>
       </c>
       <c r="E293" s="2">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>15</v>
@@ -18846,7 +18846,7 @@
         <v>9</v>
       </c>
       <c r="E294" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>15</v>
@@ -18866,7 +18866,7 @@
         <v>9</v>
       </c>
       <c r="E295" s="2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>18</v>
@@ -18886,7 +18886,7 @@
         <v>9</v>
       </c>
       <c r="E296" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>21</v>
@@ -18906,7 +18906,7 @@
         <v>9</v>
       </c>
       <c r="E297" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>10</v>
@@ -18926,7 +18926,7 @@
         <v>9</v>
       </c>
       <c r="E298" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>15</v>
@@ -18946,7 +18946,7 @@
         <v>9</v>
       </c>
       <c r="E299" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>15</v>
@@ -18966,7 +18966,7 @@
         <v>9</v>
       </c>
       <c r="E300" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>18</v>
@@ -18986,7 +18986,7 @@
         <v>9</v>
       </c>
       <c r="E301" s="2">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>21</v>
@@ -19006,7 +19006,7 @@
         <v>9</v>
       </c>
       <c r="E302" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>10</v>
@@ -19026,7 +19026,7 @@
         <v>9</v>
       </c>
       <c r="E303" s="2">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>15</v>
@@ -19046,7 +19046,7 @@
         <v>9</v>
       </c>
       <c r="E304" s="2">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>15</v>
@@ -19066,7 +19066,7 @@
         <v>9</v>
       </c>
       <c r="E305" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>18</v>
@@ -19086,7 +19086,7 @@
         <v>9</v>
       </c>
       <c r="E306" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>21</v>
@@ -19106,7 +19106,7 @@
         <v>9</v>
       </c>
       <c r="E307" s="2">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>10</v>
@@ -19126,7 +19126,7 @@
         <v>9</v>
       </c>
       <c r="E308" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>15</v>
@@ -19146,7 +19146,7 @@
         <v>9</v>
       </c>
       <c r="E309" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>15</v>
@@ -19166,7 +19166,7 @@
         <v>9</v>
       </c>
       <c r="E310" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>18</v>
@@ -19186,7 +19186,7 @@
         <v>9</v>
       </c>
       <c r="E311" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>21</v>
@@ -19206,7 +19206,7 @@
         <v>9</v>
       </c>
       <c r="E312" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>10</v>
@@ -19226,7 +19226,7 @@
         <v>9</v>
       </c>
       <c r="E313" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>15</v>
@@ -19246,7 +19246,7 @@
         <v>9</v>
       </c>
       <c r="E314" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>15</v>
@@ -19266,7 +19266,7 @@
         <v>9</v>
       </c>
       <c r="E315" s="2">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>18</v>
@@ -19286,7 +19286,7 @@
         <v>9</v>
       </c>
       <c r="E316" s="2">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>21</v>
@@ -19306,7 +19306,7 @@
         <v>9</v>
       </c>
       <c r="E317" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>10</v>
@@ -19326,7 +19326,7 @@
         <v>9</v>
       </c>
       <c r="E318" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>15</v>
@@ -19346,7 +19346,7 @@
         <v>9</v>
       </c>
       <c r="E319" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>15</v>
@@ -19366,7 +19366,7 @@
         <v>9</v>
       </c>
       <c r="E320" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>18</v>
@@ -19386,7 +19386,7 @@
         <v>9</v>
       </c>
       <c r="E321" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>21</v>
@@ -19406,7 +19406,7 @@
         <v>9</v>
       </c>
       <c r="E322" s="2">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>10</v>
@@ -19426,7 +19426,7 @@
         <v>9</v>
       </c>
       <c r="E323" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>15</v>
@@ -19446,7 +19446,7 @@
         <v>9</v>
       </c>
       <c r="E324" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>15</v>
@@ -19466,7 +19466,7 @@
         <v>9</v>
       </c>
       <c r="E325" s="2">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>18</v>
@@ -19486,7 +19486,7 @@
         <v>9</v>
       </c>
       <c r="E326" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>21</v>
@@ -19506,7 +19506,7 @@
         <v>9</v>
       </c>
       <c r="E327" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>10</v>
@@ -19526,7 +19526,7 @@
         <v>9</v>
       </c>
       <c r="E328" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>15</v>
@@ -19546,7 +19546,7 @@
         <v>9</v>
       </c>
       <c r="E329" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>15</v>
@@ -19566,7 +19566,7 @@
         <v>9</v>
       </c>
       <c r="E330" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>18</v>
@@ -19586,7 +19586,7 @@
         <v>9</v>
       </c>
       <c r="E331" s="2">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>21</v>
@@ -19606,7 +19606,7 @@
         <v>9</v>
       </c>
       <c r="E332" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>10</v>
@@ -19626,7 +19626,7 @@
         <v>9</v>
       </c>
       <c r="E333" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>15</v>
@@ -19646,7 +19646,7 @@
         <v>9</v>
       </c>
       <c r="E334" s="2">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>15</v>
@@ -19666,7 +19666,7 @@
         <v>9</v>
       </c>
       <c r="E335" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>18</v>
@@ -19686,7 +19686,7 @@
         <v>9</v>
       </c>
       <c r="E336" s="2">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>21</v>
@@ -19706,7 +19706,7 @@
         <v>9</v>
       </c>
       <c r="E337" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F337" s="2" t="s">
         <v>10</v>
@@ -19726,7 +19726,7 @@
         <v>9</v>
       </c>
       <c r="E338" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F338" s="2" t="s">
         <v>15</v>
@@ -19766,7 +19766,7 @@
         <v>9</v>
       </c>
       <c r="E340" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>18</v>
@@ -19786,7 +19786,7 @@
         <v>9</v>
       </c>
       <c r="E341" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>21</v>
@@ -19806,7 +19806,7 @@
         <v>9</v>
       </c>
       <c r="E342" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>10</v>
@@ -19826,7 +19826,7 @@
         <v>9</v>
       </c>
       <c r="E343" s="2">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F343" s="2" t="s">
         <v>15</v>
@@ -19846,7 +19846,7 @@
         <v>9</v>
       </c>
       <c r="E344" s="2">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="F344" s="2" t="s">
         <v>15</v>
@@ -19866,7 +19866,7 @@
         <v>9</v>
       </c>
       <c r="E345" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>18</v>
@@ -19886,7 +19886,7 @@
         <v>9</v>
       </c>
       <c r="E346" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>21</v>
@@ -19906,7 +19906,7 @@
         <v>9</v>
       </c>
       <c r="E347" s="2">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>10</v>
@@ -19926,7 +19926,7 @@
         <v>9</v>
       </c>
       <c r="E348" s="2">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>15</v>
@@ -19966,7 +19966,7 @@
         <v>9</v>
       </c>
       <c r="E350" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F350" s="2" t="s">
         <v>18</v>
@@ -19986,7 +19986,7 @@
         <v>9</v>
       </c>
       <c r="E351" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F351" s="2" t="s">
         <v>21</v>
@@ -20006,7 +20006,7 @@
         <v>9</v>
       </c>
       <c r="E352" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>10</v>
@@ -20026,7 +20026,7 @@
         <v>9</v>
       </c>
       <c r="E353" s="2">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>15</v>
@@ -20046,7 +20046,7 @@
         <v>9</v>
       </c>
       <c r="E354" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>15</v>
@@ -20066,7 +20066,7 @@
         <v>9</v>
       </c>
       <c r="E355" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F355" s="2" t="s">
         <v>18</v>
@@ -20086,7 +20086,7 @@
         <v>9</v>
       </c>
       <c r="E356" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F356" s="2" t="s">
         <v>21</v>
@@ -20106,7 +20106,7 @@
         <v>9</v>
       </c>
       <c r="E357" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F357" s="2" t="s">
         <v>10</v>
@@ -20126,7 +20126,7 @@
         <v>9</v>
       </c>
       <c r="E358" s="2">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>15</v>
@@ -20146,7 +20146,7 @@
         <v>9</v>
       </c>
       <c r="E359" s="2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F359" s="2" t="s">
         <v>15</v>
@@ -20166,7 +20166,7 @@
         <v>9</v>
       </c>
       <c r="E360" s="2">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>18</v>
@@ -20186,7 +20186,7 @@
         <v>9</v>
       </c>
       <c r="E361" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>21</v>
@@ -20206,7 +20206,7 @@
         <v>9</v>
       </c>
       <c r="E362" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F362" s="2" t="s">
         <v>10</v>
@@ -20226,7 +20226,7 @@
         <v>9</v>
       </c>
       <c r="E363" s="2">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F363" s="2" t="s">
         <v>15</v>
@@ -20246,7 +20246,7 @@
         <v>9</v>
       </c>
       <c r="E364" s="2">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F364" s="2" t="s">
         <v>15</v>
@@ -20266,7 +20266,7 @@
         <v>9</v>
       </c>
       <c r="E365" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F365" s="2" t="s">
         <v>18</v>
@@ -20286,7 +20286,7 @@
         <v>9</v>
       </c>
       <c r="E366" s="2">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>21</v>
@@ -20306,7 +20306,7 @@
         <v>9</v>
       </c>
       <c r="E367" s="2">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F367" s="2" t="s">
         <v>10</v>
@@ -20326,7 +20326,7 @@
         <v>9</v>
       </c>
       <c r="E368" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F368" s="2" t="s">
         <v>15</v>
@@ -20346,7 +20346,7 @@
         <v>9</v>
       </c>
       <c r="E369" s="2">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F369" s="2" t="s">
         <v>15</v>
@@ -20366,7 +20366,7 @@
         <v>9</v>
       </c>
       <c r="E370" s="2">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F370" s="2" t="s">
         <v>18</v>
@@ -20386,7 +20386,7 @@
         <v>9</v>
       </c>
       <c r="E371" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F371" s="2" t="s">
         <v>21</v>
@@ -20406,7 +20406,7 @@
         <v>9</v>
       </c>
       <c r="E372" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F372" s="2" t="s">
         <v>10</v>
@@ -20426,7 +20426,7 @@
         <v>9</v>
       </c>
       <c r="E373" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F373" s="2" t="s">
         <v>15</v>
@@ -20446,7 +20446,7 @@
         <v>9</v>
       </c>
       <c r="E374" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F374" s="2" t="s">
         <v>15</v>
@@ -20466,7 +20466,7 @@
         <v>9</v>
       </c>
       <c r="E375" s="2">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F375" s="2" t="s">
         <v>18</v>
@@ -20486,7 +20486,7 @@
         <v>9</v>
       </c>
       <c r="E376" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>21</v>
@@ -20506,7 +20506,7 @@
         <v>9</v>
       </c>
       <c r="E377" s="2">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F377" s="2" t="s">
         <v>10</v>
@@ -20526,7 +20526,7 @@
         <v>9</v>
       </c>
       <c r="E378" s="2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>15</v>
@@ -20546,7 +20546,7 @@
         <v>9</v>
       </c>
       <c r="E379" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F379" s="2" t="s">
         <v>15</v>
@@ -20566,7 +20566,7 @@
         <v>9</v>
       </c>
       <c r="E380" s="2">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F380" s="2" t="s">
         <v>18</v>
@@ -20586,7 +20586,7 @@
         <v>9</v>
       </c>
       <c r="E381" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F381" s="2" t="s">
         <v>21</v>
@@ -20606,7 +20606,7 @@
         <v>9</v>
       </c>
       <c r="E382" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>10</v>
@@ -20626,7 +20626,7 @@
         <v>9</v>
       </c>
       <c r="E383" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F383" s="2" t="s">
         <v>15</v>
@@ -20646,7 +20646,7 @@
         <v>9</v>
       </c>
       <c r="E384" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F384" s="2" t="s">
         <v>15</v>
@@ -20666,7 +20666,7 @@
         <v>9</v>
       </c>
       <c r="E385" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F385" s="2" t="s">
         <v>18</v>
@@ -20686,7 +20686,7 @@
         <v>9</v>
       </c>
       <c r="E386" s="2">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="F386" s="2" t="s">
         <v>21</v>
@@ -20706,7 +20706,7 @@
         <v>9</v>
       </c>
       <c r="E387" s="2">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F387" s="2" t="s">
         <v>10</v>
@@ -20726,7 +20726,7 @@
         <v>9</v>
       </c>
       <c r="E388" s="2">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F388" s="2" t="s">
         <v>15</v>
@@ -20746,7 +20746,7 @@
         <v>9</v>
       </c>
       <c r="E389" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F389" s="2" t="s">
         <v>15</v>
@@ -20766,7 +20766,7 @@
         <v>9</v>
       </c>
       <c r="E390" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F390" s="2" t="s">
         <v>18</v>
@@ -20786,7 +20786,7 @@
         <v>9</v>
       </c>
       <c r="E391" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F391" s="2" t="s">
         <v>21</v>
@@ -20806,7 +20806,7 @@
         <v>9</v>
       </c>
       <c r="E392" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F392" s="2" t="s">
         <v>10</v>
@@ -20826,7 +20826,7 @@
         <v>9</v>
       </c>
       <c r="E393" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F393" s="2" t="s">
         <v>15</v>
@@ -20846,7 +20846,7 @@
         <v>9</v>
       </c>
       <c r="E394" s="2">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>15</v>
@@ -20866,7 +20866,7 @@
         <v>9</v>
       </c>
       <c r="E395" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F395" s="2" t="s">
         <v>18</v>
@@ -20886,7 +20886,7 @@
         <v>9</v>
       </c>
       <c r="E396" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F396" s="2" t="s">
         <v>21</v>
@@ -20906,7 +20906,7 @@
         <v>9</v>
       </c>
       <c r="E397" s="2">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F397" s="2" t="s">
         <v>10</v>
@@ -20926,7 +20926,7 @@
         <v>9</v>
       </c>
       <c r="E398" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F398" s="2" t="s">
         <v>15</v>
@@ -20946,7 +20946,7 @@
         <v>9</v>
       </c>
       <c r="E399" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F399" s="2" t="s">
         <v>15</v>
@@ -20966,7 +20966,7 @@
         <v>9</v>
       </c>
       <c r="E400" s="2">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F400" s="2" t="s">
         <v>18</v>
@@ -20986,7 +20986,7 @@
         <v>9</v>
       </c>
       <c r="E401" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F401" s="2" t="s">
         <v>21</v>
@@ -21006,7 +21006,7 @@
         <v>9</v>
       </c>
       <c r="E402" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F402" s="2" t="s">
         <v>10</v>
@@ -21026,7 +21026,7 @@
         <v>9</v>
       </c>
       <c r="E403" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F403" s="2" t="s">
         <v>15</v>
@@ -21046,7 +21046,7 @@
         <v>9</v>
       </c>
       <c r="E404" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F404" s="2" t="s">
         <v>15</v>
@@ -21066,7 +21066,7 @@
         <v>9</v>
       </c>
       <c r="E405" s="2">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F405" s="2" t="s">
         <v>18</v>
@@ -21086,7 +21086,7 @@
         <v>9</v>
       </c>
       <c r="E406" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F406" s="2" t="s">
         <v>21</v>
@@ -21106,7 +21106,7 @@
         <v>9</v>
       </c>
       <c r="E407" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F407" s="2" t="s">
         <v>10</v>
@@ -21126,7 +21126,7 @@
         <v>9</v>
       </c>
       <c r="E408" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F408" s="2" t="s">
         <v>15</v>
@@ -21146,7 +21146,7 @@
         <v>9</v>
       </c>
       <c r="E409" s="2">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F409" s="2" t="s">
         <v>15</v>
@@ -21166,7 +21166,7 @@
         <v>9</v>
       </c>
       <c r="E410" s="2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F410" s="2" t="s">
         <v>18</v>
@@ -21186,7 +21186,7 @@
         <v>9</v>
       </c>
       <c r="E411" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F411" s="2" t="s">
         <v>21</v>
@@ -21206,7 +21206,7 @@
         <v>9</v>
       </c>
       <c r="E412" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F412" s="2" t="s">
         <v>10</v>
@@ -21226,7 +21226,7 @@
         <v>9</v>
       </c>
       <c r="E413" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F413" s="2" t="s">
         <v>15</v>
@@ -21246,7 +21246,7 @@
         <v>9</v>
       </c>
       <c r="E414" s="2">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F414" s="2" t="s">
         <v>15</v>
@@ -21266,7 +21266,7 @@
         <v>9</v>
       </c>
       <c r="E415" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F415" s="2" t="s">
         <v>18</v>
@@ -21286,7 +21286,7 @@
         <v>9</v>
       </c>
       <c r="E416" s="2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F416" s="2" t="s">
         <v>21</v>
@@ -21306,7 +21306,7 @@
         <v>9</v>
       </c>
       <c r="E417" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F417" s="2" t="s">
         <v>10</v>
@@ -21326,7 +21326,7 @@
         <v>9</v>
       </c>
       <c r="E418" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F418" s="2" t="s">
         <v>15</v>
@@ -21346,7 +21346,7 @@
         <v>9</v>
       </c>
       <c r="E419" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F419" s="2" t="s">
         <v>15</v>
@@ -21366,7 +21366,7 @@
         <v>9</v>
       </c>
       <c r="E420" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>18</v>
@@ -21406,7 +21406,7 @@
         <v>9</v>
       </c>
       <c r="E422" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F422" s="2" t="s">
         <v>10</v>
@@ -21426,7 +21426,7 @@
         <v>9</v>
       </c>
       <c r="E423" s="2">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="F423" s="2" t="s">
         <v>15</v>
@@ -21446,7 +21446,7 @@
         <v>9</v>
       </c>
       <c r="E424" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F424" s="2" t="s">
         <v>15</v>
@@ -21466,7 +21466,7 @@
         <v>9</v>
       </c>
       <c r="E425" s="2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F425" s="2" t="s">
         <v>18</v>
@@ -21486,7 +21486,7 @@
         <v>9</v>
       </c>
       <c r="E426" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F426" s="2" t="s">
         <v>21</v>
@@ -21506,7 +21506,7 @@
         <v>9</v>
       </c>
       <c r="E427" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F427" s="2" t="s">
         <v>10</v>
@@ -21526,7 +21526,7 @@
         <v>9</v>
       </c>
       <c r="E428" s="2">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F428" s="2" t="s">
         <v>15</v>
@@ -21546,7 +21546,7 @@
         <v>9</v>
       </c>
       <c r="E429" s="2">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F429" s="2" t="s">
         <v>15</v>
@@ -21566,7 +21566,7 @@
         <v>9</v>
       </c>
       <c r="E430" s="2">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F430" s="2" t="s">
         <v>18</v>
@@ -21586,7 +21586,7 @@
         <v>9</v>
       </c>
       <c r="E431" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F431" s="2" t="s">
         <v>21</v>
@@ -21606,7 +21606,7 @@
         <v>9</v>
       </c>
       <c r="E432" s="2">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F432" s="2" t="s">
         <v>10</v>
@@ -21626,7 +21626,7 @@
         <v>9</v>
       </c>
       <c r="E433" s="2">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F433" s="2" t="s">
         <v>15</v>
@@ -21646,7 +21646,7 @@
         <v>9</v>
       </c>
       <c r="E434" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F434" s="2" t="s">
         <v>15</v>
@@ -21666,7 +21666,7 @@
         <v>9</v>
       </c>
       <c r="E435" s="2">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="F435" s="2" t="s">
         <v>18</v>
@@ -21706,7 +21706,7 @@
         <v>9</v>
       </c>
       <c r="E437" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F437" s="2" t="s">
         <v>10</v>
@@ -21726,7 +21726,7 @@
         <v>9</v>
       </c>
       <c r="E438" s="2">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F438" s="2" t="s">
         <v>15</v>
@@ -21746,7 +21746,7 @@
         <v>9</v>
       </c>
       <c r="E439" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F439" s="2" t="s">
         <v>15</v>
@@ -21766,7 +21766,7 @@
         <v>9</v>
       </c>
       <c r="E440" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F440" s="2" t="s">
         <v>18</v>
@@ -21786,7 +21786,7 @@
         <v>9</v>
       </c>
       <c r="E441" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F441" s="2" t="s">
         <v>21</v>
@@ -21806,7 +21806,7 @@
         <v>9</v>
       </c>
       <c r="E442" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F442" s="2" t="s">
         <v>10</v>
@@ -21826,7 +21826,7 @@
         <v>9</v>
       </c>
       <c r="E443" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F443" s="2" t="s">
         <v>15</v>
@@ -21846,7 +21846,7 @@
         <v>9</v>
       </c>
       <c r="E444" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F444" s="2" t="s">
         <v>15</v>
@@ -21866,7 +21866,7 @@
         <v>9</v>
       </c>
       <c r="E445" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F445" s="2" t="s">
         <v>18</v>
@@ -21886,7 +21886,7 @@
         <v>9</v>
       </c>
       <c r="E446" s="2">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F446" s="2" t="s">
         <v>21</v>
@@ -21906,7 +21906,7 @@
         <v>9</v>
       </c>
       <c r="E447" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F447" s="2" t="s">
         <v>10</v>
@@ -21926,7 +21926,7 @@
         <v>9</v>
       </c>
       <c r="E448" s="2">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F448" s="2" t="s">
         <v>15</v>
@@ -21946,7 +21946,7 @@
         <v>9</v>
       </c>
       <c r="E449" s="2">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F449" s="2" t="s">
         <v>15</v>
@@ -21966,7 +21966,7 @@
         <v>9</v>
       </c>
       <c r="E450" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F450" s="2" t="s">
         <v>18</v>
@@ -21986,7 +21986,7 @@
         <v>9</v>
       </c>
       <c r="E451" s="2">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F451" s="2" t="s">
         <v>21</v>
@@ -22006,7 +22006,7 @@
         <v>9</v>
       </c>
       <c r="E452" s="2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F452" s="2" t="s">
         <v>10</v>
@@ -22026,7 +22026,7 @@
         <v>9</v>
       </c>
       <c r="E453" s="2">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F453" s="2" t="s">
         <v>15</v>
@@ -22046,7 +22046,7 @@
         <v>9</v>
       </c>
       <c r="E454" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F454" s="2" t="s">
         <v>15</v>
@@ -22066,7 +22066,7 @@
         <v>9</v>
       </c>
       <c r="E455" s="2">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F455" s="2" t="s">
         <v>18</v>
@@ -22086,7 +22086,7 @@
         <v>9</v>
       </c>
       <c r="E456" s="2">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F456" s="2" t="s">
         <v>21</v>
@@ -22106,7 +22106,7 @@
         <v>9</v>
       </c>
       <c r="E457" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F457" s="2" t="s">
         <v>10</v>
@@ -22126,7 +22126,7 @@
         <v>9</v>
       </c>
       <c r="E458" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F458" s="2" t="s">
         <v>15</v>
@@ -22146,7 +22146,7 @@
         <v>9</v>
       </c>
       <c r="E459" s="2">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F459" s="2" t="s">
         <v>15</v>
@@ -22166,7 +22166,7 @@
         <v>9</v>
       </c>
       <c r="E460" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F460" s="2" t="s">
         <v>18</v>
@@ -22186,7 +22186,7 @@
         <v>9</v>
       </c>
       <c r="E461" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F461" s="2" t="s">
         <v>21</v>
@@ -22206,7 +22206,7 @@
         <v>9</v>
       </c>
       <c r="E462" s="2">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F462" s="2" t="s">
         <v>10</v>
@@ -22226,7 +22226,7 @@
         <v>9</v>
       </c>
       <c r="E463" s="2">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F463" s="2" t="s">
         <v>15</v>
@@ -22246,7 +22246,7 @@
         <v>9</v>
       </c>
       <c r="E464" s="2">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>15</v>
@@ -22266,7 +22266,7 @@
         <v>9</v>
       </c>
       <c r="E465" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F465" s="2" t="s">
         <v>18</v>
@@ -22286,7 +22286,7 @@
         <v>9</v>
       </c>
       <c r="E466" s="2">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F466" s="2" t="s">
         <v>21</v>
@@ -22306,7 +22306,7 @@
         <v>9</v>
       </c>
       <c r="E467" s="2">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F467" s="2" t="s">
         <v>10</v>
@@ -22326,7 +22326,7 @@
         <v>9</v>
       </c>
       <c r="E468" s="2">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F468" s="2" t="s">
         <v>15</v>
@@ -22346,7 +22346,7 @@
         <v>9</v>
       </c>
       <c r="E469" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F469" s="2" t="s">
         <v>15</v>
@@ -22366,7 +22366,7 @@
         <v>9</v>
       </c>
       <c r="E470" s="2">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F470" s="2" t="s">
         <v>18</v>
@@ -22386,7 +22386,7 @@
         <v>9</v>
       </c>
       <c r="E471" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F471" s="2" t="s">
         <v>21</v>
